--- a/kvcache/unified_kv_memory/统一异构KVCache存储池_关键技术原型验证清单_V1.6_V2.3.1需求树与竞争力对齐完善版.xlsx
+++ b/kvcache/unified_kv_memory/统一异构KVCache存储池_关键技术原型验证清单_V1.6_V2.3.1需求树与竞争力对齐完善版.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,6 +297,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -855,7 +876,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>关键技术原型验证清单 V1.6｜SRS V2.2、需求树 V2.3.1 与 V3.2 竞争力分析对齐完善版</t>
+          <t>统一异构 KVCache 存储池 关键技术提前验证清单 审视结论（Mooncake 高性能原厂扩展版 V2.0）</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -865,14 +886,23 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>规范基线：SRS V2.2；分解基线：全量需求树 V2.3.1（38 SR / 203 AR）；竞争力基线：V3.2 立项论证。8 个 PVT 与 3 个 CVT 均按公平开源基线、关键消融和 E0–E3 验证阶段 (E0~E3)审阅，不预填不存在的实验结果。</t>
+          <t>【研发战略定位与评审共识】
+本项目确立“基于开源生态底座（Mooncake 与 vLLM）深度重构与架构增强，演进为面向国产 AI 硬件生态的 Mooncake 高性能原厂扩展版 (Unified KV)”的研发路线。前期借用 Mooncake 成熟的外壳接口与集群接入生态，内部深度注入原厂软硬件协同核心创新内核（Host CPU 零数据拷贝底座、C++ 描述符编译器、QueryPlan 微秒决策大脑、io_uring 裸盘直达容量主路径、6维语义强校验与多卡原子共识、DPU 硬件安全双轨与软件 Staging 组播分发），系统范围绝不框在 Mooncake 既有框架内。
+【验证架构与优先级体系 (10 PVT + 1 CVT)】
+• 🔴 P0 级（核心决胜项，5项）：PVT-02（描述符编译与异步流水）、PVT-04（微秒级动态决策）、PVT-05（HBM-SSD 直达容量主路径）、PVT-06（6维语义强校验与多卡状态同步）、PVT-07（前后台混压端到端总门禁）；
+• 🟡 P1 级（底座支撑项，4项）：PVT-00（Saved-Prefill 收益上限）、PVT-01（Host CPU 零数据拷贝底座）、PVT-03（远端直读边界与 ViewGuard）、PVT-09（DPU 硬件安全卸载加速与双轨协同）；
+• 🟢 P2 级（拓展证伪项，2项）：PVT-08（1-to-N 组播式 KV 分发拓扑）、CVT-01（PageMigration 软件 RCU 机制证伪硬件 AtomicRemap）。
+【关键场景与双轨参数扩展】
+1. 升级 PVT-08（原 CVT-01）：全面覆盖公共系统提示词广播、Multi-Agent 共享上下文分发、PD 分离 1P-to-ND 分叉三大业务场景；
+2. 升级 PVT-09（原 CVT-03）：确立 DPU 硬件安全与 Raw Direct 双轨体系，测定 500µs 无缝降级，并作为重要场景扩展提前布局 Fly-in-line 流式在途量化/压缩/CRC 软硬件双轨技术手段；
+3. 多模型双轨参数覆盖：PVT-00/02/04/07 全面支持 DeepSeek-V3/R1 (FP8 MLA 512B/tok) 与 Qwen2.5-72B (FP16 MHA 320KB/tok)；
+4. 开源基线端到端打流：全量验证基于 Mooncake Master + vLLM-Ascend 2 节点集群部署，通过官方 benchmark_serving.py 发起在线打流消融对账。</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="6" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -913,8 +943,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
@@ -995,7 +1023,6 @@
       <c r="C13" s="23" t="n"/>
       <c r="D13" s="23" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -1073,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1122,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>V1.6 关键技术原型验证总表（V2.3.1 需求树与四个核心验证阶段 (E0~E3) 对齐版）</t>
+          <t>统一异构 KVCache 存储池 关键技术提前验证总表（Mooncake 高性能原厂扩展版 10 PVT + 1 CVT 优先级精简版）</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1133,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="49" t="inlineStr">
         <is>
@@ -1185,885 +1211,856 @@
       </c>
     </row>
     <row r="5" ht="21.60000038146973" customHeight="1">
-      <c r="A5" s="51" t="n">
+      <c r="A5" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>PVT-00</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
-        <is>
-          <t>统一业务基线、收益上限与全链路观测底座</t>
-        </is>
-      </c>
-      <c r="D5" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>业务流量 Saved-Prefill 收益上限与通信加速边界评估</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🟡 P1 底座支撑)</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="55" t="inlineStr">
         <is>
           <t>IR-02-11、IR-02-12</t>
         </is>
       </c>
-      <c r="G5" s="51" t="inlineStr">
-        <is>
-          <t>IR-02-03</t>
-        </is>
-      </c>
-      <c r="H5" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】立项前必须探明目标业务流量中是否存在可复用的前缀及其理论 Saved-Prefill 收益上限。若自然复用率低或重算开销低于传输/控制开销，统一存储池形态将无商业与技术价值。
-【与项目竞争力关联】直接支撑竞争力#2（AI Infra 终极品质与 TCO 对账）与竞争力#5（公平开源对比基线）。建立统一 Trace/时钟/Telemetry 对账底座，证明“正价值复用”而非盲目 Pursue Hit Rate，为项目提供量化上行空间与退出护栏。
-【四个核心验证阶段 (E0~E3) 验证目标】E0 立项充分性；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I5" s="52" t="inlineStr">
-        <is>
-          <t>若自然复用上限不足或 TTFT/TPOT/Host CPU 零数据拷贝对账/NPU stall 无法统一观测对账，则任何传输带宽、目录命中或容量扩展都不能证明项目竞争力价值。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J5" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“离线轨迹回放 + 线上旁路影子（Shadow）观测”相结合的方法。先通过 Trace 回放建立 Saved-Prefill 理论收益曲线；再在 vLLM/SGLang 中植入轻量旁路探针，实时测算控制/传输/Attach 开销与 Saved-Prefill 的比值。
-【验证方法】1) 离线解析 Trace 提取 Reuse Distance 与前缀 overlap；2) 运行无存储池的算力重算基线（Baseline A）与开箱开源基线（Baseline B）；3) 注入网络/存储传输延时模型，计算 Net Saved-Prefill FLOPs &amp; Time；4) 进行 3 次以上重复实验校验 CV。
-【方法审阅补强】冻结同模型、同硬件、同 SLO 与统计窗口；真实 Trace 与公开/合成轨迹双轨报告，合成热点不得外推为生产结论；至少重复 3 次并给出变异系数与置信区间。</t>
-        </is>
-      </c>
-      <c r="K5" s="51" t="inlineStr">
-        <is>
-          <t>否（收益前提确认）</t>
-        </is>
-      </c>
-      <c r="L5" s="52" t="inlineStr">
-        <is>
-          <t>直接演进为 IR-02-11 的 telemetry/trace 与 IR-02-12 的 perf/CI 基线，不做一次性脚本。</t>
-        </is>
-      </c>
-      <c r="M5" s="51" t="inlineStr">
-        <is>
-          <t>MFS-0、BVG-01</t>
-        </is>
-      </c>
-      <c r="N5" s="51" t="inlineStr">
-        <is>
-          <t>4~6人日</t>
-        </is>
-      </c>
-      <c r="O5" s="51" t="inlineStr">
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-03、IR-02-02</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】Saved-Prefill 是 KVCache 存储池收益的核心前提。必须以真实业务与受控负载，实测覆盖 MLA (512B) 与 MHA (320KB) 在各复用率下的加速上限。
+【对应验证阶段】E0 业务收益确认门。</t>
+        </is>
+      </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>Saved-Prefill 净收益必须能够覆盖数据拉取、传输与挂接总开销，且在 50% 复用率下净收益 ≥ 2.0× 总开销，UBMEM 加速比 ≥ 1.30×。</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】真实/合成前缀构造 + URMA/UBMEM 对比 + 多模型矩阵消融。
+【验证方法】运行 make_workload.py 与 benchmark_serving.py 发起在线打流，采集各阶段微秒耗时。</t>
+        </is>
+      </c>
+      <c r="K5" s="55" t="inlineStr">
+        <is>
+          <t>否（立项前提收益确认项）</t>
+        </is>
+      </c>
+      <c r="L5" s="55" t="inlineStr">
+        <is>
+          <t>直接演进为 IR-02-11 的 telemetry/trace 与 IR-02-12 的 CI 性能基线。</t>
+        </is>
+      </c>
+      <c r="M5" s="55" t="inlineStr">
+        <is>
+          <t>MFS-A、BVG-01</t>
+        </is>
+      </c>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>5人日</t>
+        </is>
+      </c>
+      <c r="O5" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32.40000152587891" customHeight="1">
-      <c r="A6" s="51" t="n">
+      <c r="A6" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>PVT-01</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
-        <is>
-          <t>HBM/DDR/SSD/远端介质数据路径与完整性能力矩阵</t>
-        </is>
-      </c>
-      <c r="D6" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E6" s="51" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>Host CPU 零数据拷贝传输底座与硬件能力矩阵验证</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🟡 P1 底座支撑)</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F6" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-06、IR-01-08、IR-01-09、IR-01-12</t>
-        </is>
-      </c>
-      <c r="G6" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-07、IR-02-11</t>
-        </is>
-      </c>
-      <c r="H6" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】存储池的数据平面必须建立在真实可达、零/极低 Host Payload 参与的高性能硬件通路上。若硬件介质间数据传输依赖 CPU/DDR 显式拷贝中转，或者 completion/fence/ready 不闭环，会导致性能惨跌和数据损坏。
-【与项目竞争力关联】直接支撑竞争力#3（第一方软硬件协同与 Zero-Host-Touch 直达路径）。验证 UBMEM/URMA, RDMA, C2C, NVMe/SSD 等底层硬件原语能否真正编译为 zero Host payload touch 的 KVCache 极速传输，建立硬件能力矩阵 (Capability Matrix)。
-【四个核心验证阶段 (E0~E3) 验证目标】E1 能力路径；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I6" s="52" t="inlineStr">
-        <is>
-          <t>这是统一异构池数据平面的硬门槛；若介质不可达、隐式经过 CPU/DDR 中转、fence/ready 不闭环或错误 KV 可被消费，核心产品形态和性能叙事直接不成立。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J6" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“微基准探针（Microbench Probe）+ 硬件底层计数器 Hook + 错误注入”三位一体的方法。绕过上层框架逻辑，直接对 GPU/NPU HBM、DDR、NVMe SSD 及 RDMA/URMA 网卡注册 Memory Pool，测试原生硬件 Direct 传输带宽与 CPU cycles 开销。
-【验证方法】1) 编写零拷贝 Capability Probe 测量 P50/P99 延时与有效带宽；2) Hook 操作系统/PCIe/NIC 计数器核验 Host Payload Touch 是否为 0；3) 构造 completion-&gt;fence-&gt;integrity evidence 异步确认链；4) 注入断网/半写模拟，验证 Ready 语义屏障与错误 KV 阻断。
-【方法审阅补强】除 CPU memcpy、staged 与框架原生路径外，若目标硬件已有 Mooncake/LMCache Provider，纳入同等调优对照；强制输出计划路径与实际路径凭证（实际路径凭证（ActualPathReceipt））及 主机有效载荷触碰（Host Payload Touch）。</t>
-        </is>
-      </c>
-      <c r="K6" s="51" t="inlineStr">
-        <is>
-          <t>否（底座能力确认）</t>
-        </is>
-      </c>
-      <c r="L6" s="52" t="inlineStr">
-        <is>
-          <t>探针、注册池、句柄和microbench进入正式 Backend Provider 与CI硬件回归。</t>
-        </is>
-      </c>
-      <c r="M6" s="51" t="inlineStr">
-        <is>
-          <t>MFS-D1、MFS-D2、KTP-03、KTP-04</t>
-        </is>
-      </c>
-      <c r="N6" s="51" t="inlineStr">
-        <is>
-          <t>10~14人日</t>
-        </is>
-      </c>
-      <c r="O6" s="51" t="inlineStr">
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-06、IR-01-08、IR-01-09</t>
+        </is>
+      </c>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-12</t>
+        </is>
+      </c>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】必须确立 Host CPU 仅负责下发控制指令、不参与正文 Payload 搬运（Host Payload Touch Bytes 严格为 0）的物理底座。
+【对应验证阶段】E1 核心数据通路打通门。</t>
+        </is>
+      </c>
+      <c r="I6" s="55" t="inlineStr">
+        <is>
+          <t>打通 CANN P2P Pinning 与 URMA/UBMEM 直达，eBPF 监控 Host CPU 触碰字节严格为 0，自动导出 capability_matrix.json。</t>
+        </is>
+      </c>
+      <c r="J6" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】P2P 显存锁定 + URMA DMA + eBPF 监控零拷贝。
+【验证方法】运行 raw_trans_bench 与 host_touch_monitor.py 抓取底层传输链路带宽与 CPU 触碰。</t>
+        </is>
+      </c>
+      <c r="K6" s="55" t="inlineStr">
+        <is>
+          <t>否（物理传输底座核心项）</t>
+        </is>
+      </c>
+      <c r="L6" s="55" t="inlineStr">
+        <is>
+          <t>探针、注册池、句柄和 microbench 进入正式 Backend Provider。</t>
+        </is>
+      </c>
+      <c r="M6" s="55" t="inlineStr">
+        <is>
+          <t>KTP-03、KTP-04</t>
+        </is>
+      </c>
+      <c r="N6" s="55" t="inlineStr">
+        <is>
+          <t>6人日</t>
+        </is>
+      </c>
+      <c r="O6" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32.40000152587891" customHeight="1">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>PVT-02</t>
         </is>
       </c>
-      <c r="C7" s="52" t="inlineStr">
-        <is>
-          <t>vLLM/SGLang布局—Extent/Descriptor—异步传输流水</t>
-        </is>
-      </c>
-      <c r="D7" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E7" s="51" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>异构框架 Layout 描述符编译器与跨节点异步流水验证</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🔴 P0 核心决胜)</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F7" s="51" t="inlineStr">
+      <c r="F7" s="55" t="inlineStr">
         <is>
           <t>IR-01-02、IR-01-04</t>
         </is>
       </c>
-      <c r="G7" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-06、IR-01-08、IR-02-06</t>
-        </is>
-      </c>
-      <c r="H7" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】vLLM (PagedAttention block) 与 SGLang (RadixTree page/span) 的 KV 内存布局不一致。如果每次传输都需要逐块 CPU 编译提交或做格式转换，CPU 提交瓶颈与小 IO 放大将吞噬所有硬件带宽收益。
-【与项目竞争力关联】支撑竞争力#1（面向布局编译的 Descriptor 引擎）与竞争力#4（统一 QueryPlan 异步执行）。证明将不同框架逻辑布局编译为批量 Hardware Descriptors + 异步 DAG，可实现 Prefill/Decode 算力与 KV 传输的高效重叠。
-【四个核心验证阶段 (E0~E3) 验证目标】E1 能力路径；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I7" s="52" t="inlineStr">
-        <is>
-          <t>若需要逐块拷贝、重复后端适配或整对象同步等待，即使底层带宽达标，CPU submit、小 I/O 放大和串行等待仍会吞噬 TTFT 收益。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J7" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“逻辑 Extent 映射 -&gt; Descriptor 批量编译 -&gt; 异步 Stream/DAG 调度”的切片验证方法。构建零拷贝 Descriptor Compiler，将上层 Paged Block 映射表一次性编译为硬件 DMA/RDMA 批量描述符链表。
-【验证方法】1) 构造典型 vLLM 与 SGLang 内存布局 Manifest；2) 运行 Descriptor 编译器计算 submit CPU cycles 与 Descriptor 数量缩减比；3) 接入 PVT-01 RDMA/SSD 后端，测量 Layer/Block 级异步流水重叠率；4) 模拟 Prefill/Decode 算力 Stream 与传输 Stream 的 Concurrent 调度。
-【方法审阅补强】对照逐块拷贝、单描述符和最佳可用开源传输实现；固定布局、对象大小、队列深度与后端，拆分编译、提交、执行和等待时间，防止用大包吞吐掩盖小 I/O 放大。</t>
-        </is>
-      </c>
-      <c r="K7" s="51" t="inlineStr">
-        <is>
-          <t>否（关键执行链确认）</t>
-        </is>
-      </c>
-      <c r="L7" s="52" t="inlineStr">
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-06、IR-02-01</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】对标 vLLM-Ascend 原生 Python-ZMQ 连接器，验证 64B POD C++ 描述符批量编译与跨节点 Layerwise 边算边传异步 DAG 重叠流水。
+【对应验证阶段】E1 核心数据通路打通门。</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>描述符连续块合并压缩率 ≥ 50%，单次编译耗时 &lt; 5µs，异步 DAG 流水计算-传输重叠率 ≥ 60%，CPU 提交开销降低 ≥ 40%。</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】64B POD 描述符贪心合并 + NPU/DMA 双 Stream 异步重叠。
+【验证方法】运行 async_dag_bench 模拟 16~64 层大模型逐层边算边传。</t>
+        </is>
+      </c>
+      <c r="K7" s="55" t="inlineStr">
+        <is>
+          <t>否（架构核心决胜项）</t>
+        </is>
+      </c>
+      <c r="L7" s="55" t="inlineStr">
         <is>
           <t>原型代码直接进入 Transfer Manager 的 Descriptor/Async DAG 子模块。</t>
         </is>
       </c>
-      <c r="M7" s="51" t="inlineStr">
-        <is>
-          <t>MFS-L、KTP-09</t>
-        </is>
-      </c>
-      <c r="N7" s="51" t="inlineStr">
-        <is>
-          <t>10~12人日</t>
-        </is>
-      </c>
-      <c r="O7" s="51" t="inlineStr">
+      <c r="M7" s="55" t="inlineStr">
+        <is>
+          <t>KTP-09</t>
+        </is>
+      </c>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>8人日</t>
+        </is>
+      </c>
+      <c r="O7" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32.40000152587891" customHeight="1">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>PVT-03</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
-        <is>
-          <t>UBMEM元数据、block_table与KV direct-view安全边界</t>
-        </is>
-      </c>
-      <c r="D8" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E8" s="51" t="inlineStr">
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>远端直读 vs 显存拷贝适用边界与 ViewGuard 容错验证</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🟡 P1 底座支撑)</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-07、IR-02-04、IR-02-05</t>
+        </is>
+      </c>
+      <c r="G8" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-08</t>
+        </is>
+      </c>
+      <c r="H8" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】测定 Direct-View 与 Copy-to-HBM 的 Crossover 交叉临界点，实测证伪 Decode 阶段活跃 KV 直读，验证 ViewGuard SIGBUS 容错回滚。
+【对应验证阶段】E1/E2 路径与决策边界门。</t>
+        </is>
+      </c>
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>确立重读次数 &gt; 2 时必须 Copy-to-HBM；证实 Decode 活跃 KV 直读导致 TPOT 恶化；ViewGuard 实现 100% 捕获 SIGBUS 并安全回滚至本地重算。</t>
+        </is>
+      </c>
+      <c r="J8" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】微基准 Crossover 测定 + 真实服务注入证伪 + ViewGuard 故障演练。
+【验证方法】运行 view_vs_copy_bench 与 benchmark_serving_view.py 验证决策边界。</t>
+        </is>
+      </c>
+      <c r="K8" s="55" t="inlineStr">
+        <is>
+          <t>否（决策边界与容错核心项）</t>
+        </is>
+      </c>
+      <c r="L8" s="55" t="inlineStr">
+        <is>
+          <t>DirectViewGuard、对象分类与探针进入正式 View/Copy cost model。</t>
+        </is>
+      </c>
+      <c r="M8" s="55" t="inlineStr">
+        <is>
+          <t>KTP-10</t>
+        </is>
+      </c>
+      <c r="N8" s="55" t="inlineStr">
+        <is>
+          <t>5人日</t>
+        </is>
+      </c>
+      <c r="O8" s="55" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.60000038146973" customHeight="1">
+      <c r="A9" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>PVT-04</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>微秒级动态决策引擎与 CostEvaluator 成本模型验证</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🔴 P0 核心决胜)</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F8" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-07、IR-02-04、IR-02-05</t>
-        </is>
-      </c>
-      <c r="G8" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-10、IR-01-12、IR-02-09、IR-02-10</t>
-        </is>
-      </c>
-      <c r="H8" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】业界常误以为共享内存/UBMEM 语义可无脑用于所有 Active KV 的 Direct View（直接跨节点/跨进程远端读取）。然而 Decode 阶段重读 KV 会产生大量随机小访问，远端 Direct View 会导致严重 Page Fault、TLB Miss 和 Remote Stall。
-【与项目竞争力关联】支撑竞争力#1（语义先于位置与 View-vs-Copy 成本模型）及证伪验证。通过实测划清 Metadata/Snapshot 适合 Direct View 而 Decode Active KV 必须 Copy-to-HBM 的安全边界，防止盲目追求“零拷贝”反而损害 TPOT。
-【四个核心验证阶段 (E0~E3) 验证目标】E1/E2 路径与决策边界；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I8" s="52" t="inlineStr">
-        <is>
-          <t>UBMEM/URMA 是核心技术基础，但 PrefixDirectory、block_table 与 attention 重读 KV 的访问模式完全不同；错误地统一成 direct-view 会造成 page fault、TLB miss、remote stall 和 stale view。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J8" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“场景解耦对比（A/B Testing）+ 微观 Hardware Counter 监测 + View Guard 保护”的验证思路。将访问模式分为“只读元数据/快照”与“Decode 活跃 KV”两类，对比 Direct-View 与 Copy-to-HBM 的性能损耗。
-【验证方法】1) 使用 UBMEM/URMA 建立共享内存映射与 Direct View 句柄；2) 模拟 Attention 算子直接 View 远端 KV，抓取 CPU/NPU TLB Miss、Page Fault 及 Remote Stall 计数；3) 验证 Read-Only Lease 与 Revoke 机制；4) 计算 Cost Crossover 临界点。
-【方法审阅补强】按对象类型×访问模式做 直接访问（Direct View） 与 复制到 HBM（Copy-to-HBM） 配对 A/B；固定 page size、Rank 和重读次数，报告远端 stall/TLB/page fault，并以 View Guard 故障用例证明安全边界。</t>
-        </is>
-      </c>
-      <c r="K8" s="51" t="inlineStr">
-        <is>
-          <t>是（证伪“decode-active KV 默认 direct-view”）</t>
-        </is>
-      </c>
-      <c r="L8" s="52" t="inlineStr">
-        <is>
-          <t>DirectViewGuard、对象分类与counter探针进入正式 View/Copy cost model。</t>
-        </is>
-      </c>
-      <c r="M8" s="51" t="inlineStr">
-        <is>
-          <t>MFS-M、KTP-01、KTP-02、KTP-10</t>
-        </is>
-      </c>
-      <c r="N8" s="51" t="inlineStr">
-        <is>
-          <t>10~14人日</t>
-        </is>
-      </c>
-      <c r="O8" s="51" t="inlineStr">
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-03、IR-01-05</t>
+        </is>
+      </c>
+      <c r="G9" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-01、IR-02-02</t>
+        </is>
+      </c>
+      <c r="H9" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】构建微秒调度大脑，在微秒级时间内根据链路状态、算力与上下文长度选择最优加载或重算路径，覆盖 MLA (512B) 与 MHA。
+【对应验证阶段】E2 动态调度决策门。</t>
+        </is>
+      </c>
+      <c r="I9" s="55" t="inlineStr">
+        <is>
+          <t>单次决策耗时 P99 &lt; 5µs，决策准确率 ≥ 90%，负收益加载拦截率 100%，错误决策率 &lt; 1%。</t>
+        </is>
+      </c>
+      <c r="J9" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】5 维成本量化模型 + 微秒级剪枝 + 反事实决策对账。
+【验证方法】运行 query_plan_bench 在 100K QPS 吞吐下压测决策引擎。</t>
+        </is>
+      </c>
+      <c r="K9" s="55" t="inlineStr">
+        <is>
+          <t>否（架构核心决胜项）</t>
+        </is>
+      </c>
+      <c r="L9" s="55" t="inlineStr">
+        <is>
+          <t>原型直接演进为 PolicyEngine/PlacementResolver，复用 telemetry。</t>
+        </is>
+      </c>
+      <c r="M9" s="55" t="inlineStr">
+        <is>
+          <t>BVG-03、BVG-06、KTP-08、KTP-12</t>
+        </is>
+      </c>
+      <c r="N9" s="55" t="inlineStr">
+        <is>
+          <t>6人日</t>
+        </is>
+      </c>
+      <c r="O9" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="21.60000038146973" customHeight="1">
-      <c r="A9" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="51" t="inlineStr">
-        <is>
-          <t>PVT-04</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
-        <is>
-          <t>QueryPlan的load-vs-recompute、PlacementResolver与动态路径选择</t>
-        </is>
-      </c>
-      <c r="D9" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E9" s="51" t="inlineStr">
+    <row r="10" ht="32.40000152587891" customHeight="1">
+      <c r="A10" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>PVT-05</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>HBM-SSD 直达容量主路径与分层存储扩容验证</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🔴 P0 核心决胜)</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F9" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-03、IR-01-05</t>
-        </is>
-      </c>
-      <c r="G9" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-09、IR-02-02、IR-02-11</t>
-        </is>
-      </c>
-      <c r="H9" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】物理命中并不等于物理收益（Load 远端 KV 节点受拥塞/并发影响可能比本地算力 Prefill 重算更慢）。缺乏微秒级感知决策的存储池极易引发“负收益命中”和尾延迟恶化。
-【与项目竞争力关联】核心支撑竞争力#4（统一 QueryPlan 动态决策引擎）与竞争力#1（价值先于容量）。在微秒级内量化比较 Load, View, Move 与 Recompute 的实时 Cost，实现“正价值才加载，负收益即重算”。
-【四个核心验证阶段 (E0~E3) 验证目标】E2 决策优越性；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I9" s="52" t="inlineStr">
-        <is>
-          <t>物理命中不等于收益；若 cost model、路径选择或准入错误，远端 load 会比重算更慢并造成 abandoned hit、TTFT尾延迟和跨节点流量放大。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J9" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“离线 Oracle 轨迹对比 + 在线 Shadow QueryPlan 算法评估 + 拥塞/故障扰动”的验证方法。用低开销 EWMA 与 Hardware Telemetry 构建微秒级 Cost Evaluator，与事后最优解 (Oracle) 计算决策后悔率 (Decision Regret)。
-【验证方法】1) 收集真实硬件传输与 NPU 重算算力包络；2) 运行 QueryPlanFastPath 原型，在 &lt; 5us 内输出 Placement &amp; Action Plan；3) 注入链路拥塞与节点高负载，测试 Fallback 到重算/次优路径的决策响应；4) 统计 Cost 预测误差与错误 Load 比例。
-【方法审阅补强】同时比较静态优先级、最近副本、总是加载、总是重算和离线 Oracle；增加“关闭状态智能”和“移除非公开微架构信息”两组消融，报告 决策后悔（Decision Regret） 与错误 Load。</t>
-        </is>
-      </c>
-      <c r="K9" s="51" t="inlineStr">
-        <is>
-          <t>否（决策能力确认）</t>
-        </is>
-      </c>
-      <c r="L9" s="52" t="inlineStr">
-        <is>
-          <t>原型直接演进为 PolicyEngine/PlacementResolver，并复用路径telemetry。</t>
-        </is>
-      </c>
-      <c r="M9" s="51" t="inlineStr">
-        <is>
-          <t>MFS-B、BVG-03、BVG-06、KTP-08、KTP-12</t>
-        </is>
-      </c>
-      <c r="N9" s="51" t="inlineStr">
-        <is>
-          <t>8~10人日</t>
-        </is>
-      </c>
-      <c r="O9" s="51" t="inlineStr">
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-01、IR-02-08、IR-02-09</t>
+        </is>
+      </c>
+      <c r="G10" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-09</t>
+        </is>
+      </c>
+      <c r="H10" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】对标 Mooncake 原生文件级 SSD Offload，验证 Linux 6.6+ io_uring FIXED I/O 裸盘直达容量主路径，在显存超载下实现安全扩容。
+【对应验证阶段】E2 分层扩容与容量门。</t>
+        </is>
+      </c>
+      <c r="I10" s="55" t="inlineStr">
+        <is>
+          <t>在 150% 显存超载下，系统支持的可服务容量提升 ≥ 30%，OOM 发生率降低 ≥ 50%，SSD 直达吞吐达硬件线速 ≥ 80%，全程 Bypass DDR。</t>
+        </is>
+      </c>
+      <c r="J10" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】裸盘 4KB 对齐管理 + io_uring Direct I/O + 水位线驱动异步沉淀。
+【验证方法】运行 tier_storage_bench 与 benchmark_tiering.py 进行超载压测。</t>
+        </is>
+      </c>
+      <c r="K10" s="55" t="inlineStr">
+        <is>
+          <t>否（架构核心决胜项）</t>
+        </is>
+      </c>
+      <c r="L10" s="55" t="inlineStr">
+        <is>
+          <t>回放器与策略接口进入 TierManager，冻结硬件容量投入边界。</t>
+        </is>
+      </c>
+      <c r="M10" s="55" t="inlineStr">
+        <is>
+          <t>BVG-04、BVG-08、KTP-03、KTP-06、KTP-07、KTP-17</t>
+        </is>
+      </c>
+      <c r="N10" s="55" t="inlineStr">
+        <is>
+          <t>6人日</t>
+        </is>
+      </c>
+      <c r="O10" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32.40000152587891" customHeight="1">
-      <c r="A10" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="51" t="inlineStr">
-        <is>
-          <t>PVT-05</t>
-        </is>
-      </c>
-      <c r="C10" s="52" t="inlineStr">
-        <is>
-          <t>统一池分层容量、DDR角色与KV生命周期策略</t>
-        </is>
-      </c>
-      <c r="D10" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E10" s="51" t="inlineStr">
+    <row r="11" ht="32.40000152587891" customHeight="1">
+      <c r="A11" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>PVT-06</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>多维度语义一致性强校验与 TP=8 多卡状态同步验证</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🔴 P0 核心决胜)</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F10" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-01、IR-02-08、IR-02-09</t>
-        </is>
-      </c>
-      <c r="G10" s="51" t="inlineStr">
-        <is>
-          <t>IR-02-02</t>
-        </is>
-      </c>
-      <c r="H10" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】HBM 昂贵且容量有限，必须利用 NVMe SSD 扩展可寻址容量。但可寻址容量不等于可服务能力；若分层搬运造成 HBM 碎片、Preemption 抖动或 DDR 缓存无效命中，将严重损害 QPS 与成本效益。
-【与项目竞争力关联】核心支撑竞争力#1（分层容量与 DDR 条件角色）与竞争力#2（可服务容量与 NPU 吞吐提升）。验证“HBM↔SSD 直通为容量主路径，DDR 仅承担正收益条件角色”，确保每一 GB 扩展容量都转化为实际业务 QPS。
-【四个核心验证阶段 (E0~E3) 验证目标】E2/E3 决策与系统净收益；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I10" s="52" t="inlineStr">
-        <is>
-          <t>可寻址字节增加不等于服务容量增加；若碎片、preemption、迁移抖动或DDR成本抵消收益，统一池最核心的容量价值无法成立。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J10" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“离线策略回放器（Replayer）+ 真实受控物理介质压测”相结合的验证思路。对比 HBM↔SSD 直达、HBM→DDR→SSD 三级传递、DDR Warm/Prefetch 等不同架构模式下的吞吐与延迟。
-【验证方法】1) 运行 Trace 驱动的容量策略回放器，对比 LRU, LFU, Cost-aware 淘汰算法；2) 在真实 HBM+DDR+SSD 硬件节点配置受控内存/存储水位；3) 测量 HBM 有效容量提升、OOM/Preemption 降低率与 SSD 读写 IOPS/写放大；4) 评估 DDR 引入后的净收益 (Cost-Benefit Ratio)。
-【方法审阅补强】比较简单双水位、LRU/LFU 与成本策略；除容量和命中外同步报告 TPOT、SSD IOPS/写放大、功耗和单位 SLO 合格事务成本，防止成本转移。</t>
-        </is>
-      </c>
-      <c r="K10" s="51" t="inlineStr">
-        <is>
-          <t>否（容量价值确认）</t>
-        </is>
-      </c>
-      <c r="L10" s="52" t="inlineStr">
-        <is>
-          <t>回放器与策略接口进入TierManager；实验结论冻结硬件容量和人力投入边界。</t>
-        </is>
-      </c>
-      <c r="M10" s="51" t="inlineStr">
-        <is>
-          <t>MFS-R、BVG-04、BVG-08、KTP-06、KTP-07、KTP-17</t>
-        </is>
-      </c>
-      <c r="N10" s="51" t="inlineStr">
-        <is>
-          <t>10~14人日</t>
-        </is>
-      </c>
-      <c r="O10" s="51" t="inlineStr">
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-10、IR-01-11、IR-02-01</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>IR-02-05、IR-02-10</t>
+        </is>
+      </c>
+      <c r="H11" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】验证 6 维语义（模型/词表/模板/LoRA/Ready/Lease）微秒级强校验，杜绝脏读；验证 TP=8 张量并行多卡共享内存状态同步耗时 P99 &lt; 100µs。
+【对应验证阶段】E1 核心数据通路打通门。</t>
+        </is>
+      </c>
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>8 类语义冲突拦截率 100%，错误消费严格为 0；TP=8 多卡状态同步耗时 P99 &lt; 100µs，杜绝集合通信死锁与部分命中挂死。</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】xxHash64 6 维校验 + POSIX /dev/shm 共享内存状态广播 + 协同 Fallback。
+【验证方法】运行 rank_consensus_bench 与 test_correctness.py 进行故障注入。</t>
+        </is>
+      </c>
+      <c r="K11" s="55" t="inlineStr">
+        <is>
+          <t>否（架构核心决胜项）</t>
+        </is>
+      </c>
+      <c r="L11" s="55" t="inlineStr">
+        <is>
+          <t>协议、判定器、golden cases 与 fault tests 进入 Connector/Directory 正式模块。</t>
+        </is>
+      </c>
+      <c r="M11" s="55" t="inlineStr">
+        <is>
+          <t>BVG-02、BVG-07</t>
+        </is>
+      </c>
+      <c r="N11" s="55" t="inlineStr">
+        <is>
+          <t>6人日</t>
+        </is>
+      </c>
+      <c r="O11" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32.40000152587891" customHeight="1">
-      <c r="A11" s="51" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>PVT-06</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr">
-        <is>
-          <t>Raw Hit→Usable Hit→Attach/Partial Reuse的正确性闭环</t>
-        </is>
-      </c>
-      <c r="D11" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E11" s="51" t="inlineStr">
+    <row r="12" ht="21.60000038146973" customHeight="1">
+      <c r="A12" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>PVT-07</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>前后台混压全链路端到端总门禁与 SemanticQoS 验证</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🔴 P0 核心决胜)</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
         <is>
           <t>K0</t>
         </is>
       </c>
-      <c r="F11" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-10、IR-01-11、IR-02-01、IR-02-05</t>
-        </is>
-      </c>
-      <c r="G11" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-12、IR-02-03、IR-02-04、IR-02-09、IR-02-10</t>
-        </is>
-      </c>
-      <c r="H11" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】物理 Raw Hit 绝不等于可安全消费的 Usable Hit。若 KV 存在版本冲突、Layout 不匹配、Rank 未对齐、未 Ready 或 Lease 过期，强行消费将导致输出胡言乱语、死锁甚至跨租户数据泄露事故。
-【与项目竞争力关联】核心支撑竞争力#1（语义先于位置与 Ready/Eligibility 屏障）与竞争力#2（0 错误消费正确性安全底线）。构建完整的 ConsumeEligibility 与 Rank Consensus 校验机制，确保“0 错误消费、0 过期消费”。
-【四个核心验证阶段 (E0~E3) 验证目标】E1 可消费正确性；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I11" s="52" t="inlineStr">
-        <is>
-          <t>项目价值取决于 usable hit，而不是 raw hit；任何错误或过期 KV 被 attach 都会形成正确性事故，多 rank 不一致还会造成死锁或隐蔽错误。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J11" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“语义契约断言校验 + 故障/冲突全量注入 + 张量并行 (TP=8) 多卡状态同步 (RankConsensus)”的硬核正确性验证思路。设计 Reason-Code 判定引擎，对每一个 Candidate KV 进行 6 维 Eligibility 检查。
-【验证方法】1) 构造全套正确的 Golden Cases 与带冲突的 Fault Injection Cases；2) 运行 ConsumeEligibility &amp; AttachHandle 校验模块；3) 验证多 Rank 间 RankConsensus 屏障与 Wait 时延；4) 统计 Raw Hit 到 Usable Hit 的转化漏斗与 Duplicate Pull 合并效率。
-【方法审阅补强】使用 Golden/Fault 全矩阵覆盖版本、布局、Ready、Lease、Rank 和跨租户；与原生/最佳开源连接器的兼容与回退行为对照，任何错误消费均直接 No-Go。</t>
-        </is>
-      </c>
-      <c r="K11" s="51" t="inlineStr">
-        <is>
-          <t>否（可消费性确认）</t>
-        </is>
-      </c>
-      <c r="L11" s="52" t="inlineStr">
-        <is>
-          <t>协议、判定器、golden cases与fault tests进入Connector/Directory正式模块。</t>
-        </is>
-      </c>
-      <c r="M11" s="51" t="inlineStr">
-        <is>
-          <t>BVG-02、BVG-07</t>
-        </is>
-      </c>
-      <c r="N11" s="51" t="inlineStr">
-        <is>
-          <t>10~12人日</t>
-        </is>
-      </c>
-      <c r="O11" s="51" t="inlineStr">
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-04、IR-01-11、IR-02-06</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-12、IR-02-02、IR-02-07、IR-02-11</t>
+        </is>
+      </c>
+      <c r="H12" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】在真实 2 节点集群、前台在线推理与后台 400G I/O 满载混压下，串联全流程，实施三重消融对账，确立立项总门禁。
+【对应验证阶段】E3 全链路前后台混压总门禁。</t>
+        </is>
+      </c>
+      <c r="I12" s="55" t="inlineStr">
+        <is>
+          <t>深度重构扩展版相比官方原生 Mooncake，全链路 P99 TTFT 降低 ≥ 20%，QPS 提升 ≥ 10%，后台混压下前台 P99 TPOT 干扰率严格 &lt; 3%。</t>
+        </is>
+      </c>
+      <c r="J12" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】2 节点真实集群 + 官方 benchmark_serving.py 在线打流 + 三重消融总门禁。
+【验证方法】运行 deploy_cluster.sh 与 run_mixed_bench.py 执行全链路压测。</t>
+        </is>
+      </c>
+      <c r="K12" s="55" t="inlineStr">
+        <is>
+          <t>否（项目价值总门禁）</t>
+        </is>
+      </c>
+      <c r="L12" s="55" t="inlineStr">
+        <is>
+          <t>端到端最小闭环成为首个系统串联与回归场景；QoS 分类与接口进入正式系统。</t>
+        </is>
+      </c>
+      <c r="M12" s="55" t="inlineStr">
+        <is>
+          <t>MFS-B、BVG-03、BVG-05、KTP-11</t>
+        </is>
+      </c>
+      <c r="N12" s="55" t="inlineStr">
+        <is>
+          <t>8人日</t>
+        </is>
+      </c>
+      <c r="O12" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21.60000038146973" customHeight="1">
-      <c r="A12" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="51" t="inlineStr">
-        <is>
-          <t>PVT-07</t>
-        </is>
-      </c>
-      <c r="C12" s="52" t="inlineStr">
-        <is>
-          <t>前后台QoS、计算—传输重叠与全链路端到端最小闭环验证</t>
-        </is>
-      </c>
-      <c r="D12" s="51" t="inlineStr">
-        <is>
-          <t>立项前必做</t>
-        </is>
-      </c>
-      <c r="E12" s="51" t="inlineStr">
-        <is>
-          <t>K0</t>
-        </is>
-      </c>
-      <c r="F12" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-04、IR-01-11、IR-02-06</t>
-        </is>
-      </c>
-      <c r="G12" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-12、IR-02-02、IR-02-07、IR-02-11</t>
-        </is>
-      </c>
-      <c r="H12" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】单项传输带宽或局部算法达标，不代表在线系统成功。在真实在线推理中，前台 Decode 算力/带宽与后台 SSD 回源、预取、迁移混压，极易引发 IO 争用与 TPOT 尾部严重抖动。
-【与项目竞争力关联】终极支撑竞争力#2（端到端净收益与端到端最小闭环验证 (Vertical Slice)验收）与竞争力#4（前后台 Semantic QoS 隔离）。作为立项前最后一个“纵向切片”总门禁，在真实混压下验证 TTFT/TPOT/QPS 整体净收益。
-【四个核心验证阶段 (E0~E3) 验证目标】E3 系统净收益；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I12" s="52" t="inlineStr">
-        <is>
-          <t>单项带宽或算法达标不代表在线业务成功；共享 RNIC、DMA、内存带宽和 copy stream 的干扰可能把容量与命中收益全部抵消。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J12" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“真实前后台混压（Co-location Stress）+ 端到端纵向切片（Vertical Slice）+ 前后台服务质量保障策略 (SemanticQoS)判定”的闭环验证思路。串联 Prefix Lookup -&gt; QueryPlan -&gt; Descriptor -&gt; Load/Attach/Recompute 全流程。
-【验证方法】1) 建立包含前台 Decode 推理与后台 SSD 回源/Prefetch 的混压环境；2) 运行 Semantic QoS 调度策略，设定前后台优先级与限速包络；3) 抓取端到端 TTFT P50/P99、TPOT P50/P99/Tail Spike、QPS 及 NPU Busy/Stall；4) 执行 Fallback 演练。
-【方法审阅补强】在同硬件、同模型、同 SLO、同调优预算下比较原生框架、最佳可行开源组合、本项目关闭状态智能、本项目移除微架构信息及完整方案；以实际路径、合格业务事务和全生命周期成本给出净收益。</t>
-        </is>
-      </c>
-      <c r="K12" s="51" t="inlineStr">
-        <is>
-          <t>否（项目价值总门禁）</t>
-        </is>
-      </c>
-      <c r="L12" s="52" t="inlineStr">
-        <is>
-          <t>端到端最小闭环验证 (Vertical Slice) 成为首个系统串联与回归场景；QoS分类、指标和fallback接口直接进入正式系统。</t>
-        </is>
-      </c>
-      <c r="M12" s="51" t="inlineStr">
-        <is>
-          <t>MFS-B、BVG-03、BVG-05、KTP-11</t>
-        </is>
-      </c>
-      <c r="N12" s="51" t="inlineStr">
-        <is>
-          <t>12~15人日</t>
-        </is>
-      </c>
-      <c r="O12" s="51" t="inlineStr">
+    <row r="13" ht="21.60000038146973" customHeight="1">
+      <c r="A13" s="55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>PVT-08</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>1-to-N 组播式 KV 分发：硬件多播 vs 软件分层中继验证</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🟢 P2 拓展证伪)</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-04、IR-01-10</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-09</t>
+        </is>
+      </c>
+      <c r="H13" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】覆盖公共系统提示词广播、Multi-Agent 共享上下文分发、PD 分离 1P-to-ND 分叉三大业务场景，验证软件 Staging 组播相比单播源端带宽节省 ≥ 60%。
+【对应验证阶段】E1 拓展分发拓扑验证门。</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="inlineStr">
+        <is>
+          <t>在 1-to-8 分发下，软件 Staging 组播相比单播源端带宽节省 ≥ 60%，传输耗时降低 ≥ 40%，且在硬件多播不可用时作为高可用主力路径。</t>
+        </is>
+      </c>
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】三大场景流量编排 + 单播 vs 软件 Staging 树状分发 vs 硬件多播对比。
+【验证方法】运行 multicast_fanout_bench.cc 测量不同节点规模下的分发时延与带宽。</t>
+        </is>
+      </c>
+      <c r="K13" s="55" t="inlineStr">
+        <is>
+          <t>否 (原 CVT-01 升级为必做项)</t>
+        </is>
+      </c>
+      <c r="L13" s="55" t="inlineStr">
+        <is>
+          <t>软件 Staging 拓扑管理与树状分发算法进入 Transfer Manager 组播子模块。</t>
+        </is>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>KTP-14</t>
+        </is>
+      </c>
+      <c r="N13" s="55" t="inlineStr">
+        <is>
+          <t>4人日</t>
+        </is>
+      </c>
+      <c r="O13" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.60000038146973" customHeight="1">
-      <c r="A13" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="51" t="inlineStr">
+    <row r="14" ht="32.40000152587891" customHeight="1">
+      <c r="A14" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>PVT-09</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>DPU 硬件安全与算力卸载加速 vs Raw Direct 双轨验证</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>立项前必做 (🟡 P1 底座支撑)</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-08、IR-01-09</t>
+        </is>
+      </c>
+      <c r="G14" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-12</t>
+        </is>
+      </c>
+      <c r="H14" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】确立公有云可信 VPC 下 Raw Direct 纯软主路径与企业级专线下 DPU 硬件线速 AES/CRC 卸载的双轨体系；验证 500µs 无缝降级；提前布局 Fly-in-line 在途处理。
+【对应验证阶段】E1 底座支撑与双轨验证门。</t>
+        </is>
+      </c>
+      <c r="I14" s="55" t="inlineStr">
+        <is>
+          <t>DPU 硬件线速完成 AES-256/CRC64 卸载（CPU 占用降 ≥ 30%）；注入 DPU 故障时系统在 &lt; 500µs 内无缝降级至 Raw Direct 裸机直达路径，业务不中断。</t>
+        </is>
+      </c>
+      <c r="J14" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】Raw Direct 基线 + DPU 硬件加速 A/B 测试 + 500µs 降级演练 + Fly-in-line 架构布局。
+【验证方法】运行 offload_fallback_bench 与 inject_dpu_fault.py 演练双轨切换。</t>
+        </is>
+      </c>
+      <c r="K14" s="55" t="inlineStr">
+        <is>
+          <t>否 (原 CVT-03 升级为必做项)</t>
+        </is>
+      </c>
+      <c r="L14" s="55" t="inlineStr">
+        <is>
+          <t>双轨切换引擎与安全卸载插件进入 Backend Provider 模块。</t>
+        </is>
+      </c>
+      <c r="M14" s="55" t="inlineStr">
+        <is>
+          <t>KTP-13、KTP-16</t>
+        </is>
+      </c>
+      <c r="N14" s="55" t="inlineStr">
+        <is>
+          <t>5人日</t>
+        </is>
+      </c>
+      <c r="O14" s="55" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21.60000038146973" customHeight="1">
+      <c r="A15" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>CVT-01</t>
         </is>
       </c>
-      <c r="C13" s="52" t="inlineStr">
-        <is>
-          <t>多消费者一次加载与1→N多播/fanout边界</t>
-        </is>
-      </c>
-      <c r="D13" s="51" t="inlineStr">
-        <is>
-          <t>条件/证伪</t>
-        </is>
-      </c>
-      <c r="E13" s="51" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>PageMigration 软件 RCU 机制 vs 硬件 AtomicRemap 必要性证伪</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>条件/证伪 (🟢 P2 拓展证伪)</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="F13" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-04、IR-01-10</t>
-        </is>
-      </c>
-      <c r="G13" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】业界常推崇硬件多播 (Multicast) 用于热点前缀分发。但硬件多播配置复杂且依赖网络支持，必须验证节点级 Staging / 软件 Fanout 是否已足够满足要求，证伪硬件多播的“硬依赖”假象。
-【与项目竞争力关联】支撑竞争力#5（开放生态与简洁架构）及条件证伪。明确 1→N 共享的 Crossover 点，避免在立项早期过度投入复杂硬件多播。
-【四个核心验证阶段 (E0~E3) 验证目标】条件证伪门；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I13" s="52" t="inlineStr">
-        <is>
-          <t>只在真实 fanout 高且重复远端字节成为瓶颈时影响 IR；否则不应提前占用主线人力。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J13" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“Fanout 规模阶梯对比 + 传输放大系数测量 + 硬件多播必要性证伪”的验证思路。
-【验证方法】1) 构造不同 Fanout 比例的并发拉取请求；2) 测量源端 egress 带宽与各 Consumer 端完成时间 P99；3) 评估软件 Staging 与硬件多播的收益差距；4) 判定 Fanout Crossover 临界点。
-【方法审阅补强】仅在 Fanout 分布和重复远端字节达到触发门后执行；比较 N 次独立拉取、软件 Staging 和硬件多播，硬件能力无稳定增量即关闭。</t>
-        </is>
-      </c>
-      <c r="K13" s="51" t="inlineStr">
-        <is>
-          <t>是（证伪“硬件多播是关键IR前置条件”）</t>
-        </is>
-      </c>
-      <c r="L13" s="52" t="inlineStr">
-        <is>
-          <t>仅Go后进入Async DAG的可选Multicast Provider。</t>
-        </is>
-      </c>
-      <c r="M13" s="51" t="inlineStr">
-        <is>
-          <t>KTP-14</t>
-        </is>
-      </c>
-      <c r="N13" s="51" t="inlineStr">
-        <is>
-          <t>6~8人日（触发后）</t>
-        </is>
-      </c>
-      <c r="O13" s="51" t="inlineStr">
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-01、IR-01-11</t>
+        </is>
+      </c>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>IR-01-12</t>
+        </is>
+      </c>
+      <c r="H15" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】验证在显存整理与页迁移时，软件 RCU + Copy-on-Migrate 是否已能满足 Pause &lt; 1ms 要求，证明无需强依赖专有硬件 AtomicRemap 芯片。
+【对应验证阶段】条件证伪门。</t>
+        </is>
+      </c>
+      <c r="I15" s="55" t="inlineStr">
+        <is>
+          <t>在 32 并发 Reader 下，软件 RCU 读停顿时间 P99 &lt; 1ms，TPOT 抖动率 &lt; 3%，免除对专有硬件 AtomicRemap 芯片的强依赖。</t>
+        </is>
+      </c>
+      <c r="J15" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】并发读写压测 + Pause 抖动抓取 + 软硬件收益对比证伪。
+【验证方法】运行 rcu_migration_bench.cc 测量高并发 Reader 下的迁移停顿与 Jitter。</t>
+        </is>
+      </c>
+      <c r="K15" s="55" t="inlineStr">
+        <is>
+          <t>是 (原 CVT-02 重新编号为 CVT-01)</t>
+        </is>
+      </c>
+      <c r="L15" s="55" t="inlineStr">
+        <is>
+          <t>软件 RCU 原型作为显存整理与动态页迁移的正式核心机制保留。</t>
+        </is>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>KTP-15</t>
+        </is>
+      </c>
+      <c r="N15" s="55" t="inlineStr">
+        <is>
+          <t>3人日</t>
+        </is>
+      </c>
+      <c r="O15" s="55" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.40000152587891" customHeight="1">
-      <c r="A14" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="51" t="inlineStr">
-        <is>
-          <t>CVT-02</t>
-        </is>
-      </c>
-      <c r="C14" s="52" t="inlineStr">
-        <is>
-          <t>atomic remap/page migration相对软件RCU的必要性</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="inlineStr">
-        <is>
-          <t>条件/证伪</t>
-        </is>
-      </c>
-      <c r="E14" s="51" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="F14" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-01、IR-01-11、IR-01-12</t>
-        </is>
-      </c>
-      <c r="G14" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】内存页迁移/压缩时，业界探索硬件 Atomic Remap 原语。需验证软件 RCU (Read-Copy-Update) + Copy-on-Migrate 是否已能满足 Pause 与抖动要求，优先证伪硬件原语的“必需性”。
-【与项目竞争力关联】支撑竞争力#3（第一方软硬件协同的理性边界）。防范盲目依赖未成熟硬件原语导致架构套牢。
-【四个核心验证阶段 (E0~E3) 验证目标】条件证伪门；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I14" s="52" t="inlineStr">
-        <is>
-          <t>该能力仅在迁移/压紧 pause 成为已证实瓶颈时决定 IR 实现；否则属于 P2/P3 平台优化。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J14" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“读写并发压测 + Pause 抖动抓取 + 失败回滚演练”的验证思路。
-【验证方法】1) 在 Reader 持续读取 KV 时触发 Extent 迁移/整理；2) 测量 Reader 的 Pause 时间 P99 与 TPOT Jitter；3) 注入 Remap 中途中断，验证崩溃回滚；4) 评估 RCU 与硬件 Remap 的增量收益。
-【方法审阅补强】以软件 RCU + Copy-on-Migrate 为默认基线，覆盖并发读、故障中断、回滚和 TLB shootdown；硬件 Remap 只接受可重复的增量收益。</t>
-        </is>
-      </c>
-      <c r="K14" s="51" t="inlineStr">
-        <is>
-          <t>是（优先证伪硬件原语必要性）</t>
-        </is>
-      </c>
-      <c r="L14" s="52" t="inlineStr">
-        <is>
-          <t>仅Go后把硬件remap作为feature-flag后端；RCU原型直接保留。</t>
-        </is>
-      </c>
-      <c r="M14" s="51" t="inlineStr">
-        <is>
-          <t>KTP-15</t>
-        </is>
-      </c>
-      <c r="N14" s="51" t="inlineStr">
-        <is>
-          <t>8~12人日（触发后）</t>
-        </is>
-      </c>
-      <c r="O14" s="51" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21.60000038146973" customHeight="1">
-      <c r="A15" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="51" t="inlineStr">
-        <is>
-          <t>CVT-03</t>
-        </is>
-      </c>
-      <c r="C15" s="52" t="inlineStr">
-        <is>
-          <t>DPU/CQ/硬件codec卸载的可用性与净收益</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>条件/证伪</t>
-        </is>
-      </c>
-      <c r="E15" s="51" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="F15" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-08、IR-01-09</t>
-        </is>
-      </c>
-      <c r="G15" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-12</t>
-        </is>
-      </c>
-      <c r="H15" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】评估 DPU 卸载、硬件 CQ 路由与硬件 Codec 压缩的真实价值。需明确项目在无 DPU/Codec 时必须按 Raw/Direct 路径完全成立，且严禁使用 Host CPU 软件压缩/全量 CPU CRC 填补缺口。
-【与项目竞争力关联】支撑竞争力#3（第一方责任与防伪解耦）及能力降级验证。确保主路径纯粹高效，任何卸载只能是“纯增量”而非“硬依附”。
-【四个核心验证阶段 (E0~E3) 验证目标】条件证伪门；当前仅验证潜在优势，未达 E3 不宣称优于最佳开源替代。</t>
-        </is>
-      </c>
-      <c r="I15" s="52" t="inlineStr">
-        <is>
-          <t>DPU与硬件 codec 是可选加速而非统一池成立前提；只有平台真实提供且 Host CPU/CQ/存储带宽成为瓶颈时才需要验证。
-【决策约束】结论必须能改变首发范围、默认路径、功能开关、采购或人力，不能只证明局部指标。</t>
-        </is>
-      </c>
-      <c r="J15" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“Raw Direct 基线对比 + DPU/Codec 硬件卸载 A/B 测试 + CPU 软解压对比防误区”的验证思路。
-【验证方法】1) 以 PVT-01 Raw Direct 路径为绝对 Baseline；2) 接入 DPU/硬件 Codec，测量 Host CPU 卸载比例与 CQ 提交延时；3) 故意关闭 DPU/Codec，测试无缝 Fallback 到 Raw Direct 路径；4) 评估 CPU 软件 Codec 对 CPU 的吞噬副作用。
-【方法审阅补强】以无 DPU/Codec 的 原始直达（Raw Direct） 为必须成立基线；DPU/Codec 只验证纯增量并执行关闭/故障旁路，禁止以 CPU 软件编解码伪造收益。</t>
-        </is>
-      </c>
-      <c r="K15" s="51" t="inlineStr">
-        <is>
-          <t>是（证伪“DPU/codec是项目必需依赖”）</t>
-        </is>
-      </c>
-      <c r="L15" s="52" t="inlineStr">
-        <is>
-          <t>仅Go后作为Backend Provider可选插件；主路径保持无DPU可运行。</t>
-        </is>
-      </c>
-      <c r="M15" s="51" t="inlineStr">
-        <is>
-          <t>KTP-13、KTP-16</t>
-        </is>
-      </c>
-      <c r="N15" s="51" t="inlineStr">
-        <is>
-          <t>5~8人日（触发后）</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
@@ -2094,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2119,7 +2116,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>关键技术最小原型验证设计（V1.6 / V2.3.1 / 四个核心验证阶段 (E0~E3) 对齐版）</t>
+          <t>统一异构 KVCache 存储池 关键技术提前验证详细设计（Mooncake 高性能原厂扩展版 10 PVT + 1 CVT）</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2127,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="49" t="inlineStr">
         <is>
@@ -2224,1072 +2220,691 @@
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>PVT-00</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】立项前必须探明目标业务流量中是否存在可复用的前缀及其理论 Saved-Prefill 收益上限。若自然复用率低或重算开销低于传输/控制开销，统一存储池形态将无商业与技术价值。
-【与项目竞争力关联】直接支撑竞争力#2（AI Infra 终极品质与 TCO 对账）与竞争力#5（公平开源对比基线）。建立统一 Trace/时钟/Telemetry 对账底座，证明“正价值复用”而非盲目 Pursue Hit Rate，为项目提供量化上行空间与退出护栏。
-【对应验证阶段 (E0~E3)】E0 立项充分性。</t>
-        </is>
-      </c>
-      <c r="C5" s="52" t="inlineStr">
-        <is>
-          <t>抽取 1~3 天代表性业务脱敏 Trace（拿不到时使用 ShareGPT + Zipf 长上下文合成轨迹双轨替代）。冻结模型 (Qwen/Llama/DeepSeek 架构)、tokenizer、chat template、layout、并发 (1~128)、拓扑与到达分布；上下文涵盖 4K/32K/128K/256K+；为 vLLM/SGLang 建立统一时间戳、raw/usable/abandoned hit、Host Payload touch、NPU busy/stall 与 fallback 数据采集。</t>
-        </is>
-      </c>
-      <c r="D5" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“离线轨迹回放 + 线上旁路影子（Shadow）观测”相结合的方法。先通过 Trace 回放建立 Saved-Prefill 理论收益曲线；再在 vLLM/SGLang 中植入轻量旁路探针，实时测算控制/传输/Attach 开销与 Saved-Prefill 的比值。
-【验证方法】1) 离线解析 Trace 提取 Reuse Distance 与前缀 overlap；2) 运行无存储池的算力重算基线（Baseline A）与开箱开源基线（Baseline B）；3) 注入网络/存储传输延时模型，计算 Net Saved-Prefill FLOPs &amp; Time；4) 进行 3 次以上重复实验校验 CV。
-【方法审阅补强】冻结同模型、同硬件、同 SLO 与统计窗口；真实 Trace 与公开/合成轨迹双轨报告，合成热点不得外推为生产结论；至少重复 3 次并给出变异系数与置信区间。</t>
-        </is>
-      </c>
-      <c r="E5" s="52" t="inlineStr">
-        <is>
-          <t>2 个框架；1 个主模型；4 档上下文（4K/32K/128K/256K+）；3 档并发；同一 case 重复≥3次。</t>
-        </is>
-      </c>
-      <c r="F5" s="52" t="inlineStr">
-        <is>
-          <t>重算/原生框架；vLLM/SGLang 原生 prefix cache/offload 开关；若可用，最佳可行开源组合；所有后续 PVT 共用冻结基线。</t>
-        </is>
-      </c>
-      <c r="G5" s="52" t="inlineStr">
-        <is>
-          <t>可复用请求/token占比、prefix P50/P95、reuse distance、容量—命中曲线、理论 saved-prefill、TTFT分解、TPOT、NPU busy/stall、Host CPU 零数据拷贝对账、指标丢失率、重复实验CV。</t>
-        </is>
-      </c>
-      <c r="H5" s="52" t="inlineStr">
-        <is>
-          <t>至少一个明确业务分层的 P95 Saved-Prefill 预算 ≥ 控制+传输+Attach 预算的 2 倍；核心指标丢失率 &lt; 0.1%，重复实验 CV &lt; 5%。</t>
-        </is>
-      </c>
-      <c r="I5" s="52" t="inlineStr">
-        <is>
-          <t>收益仅集中于特定模板/租户（如 Code/Agent 多轮会话），项目限定场景立项并冻结白名单。</t>
-        </is>
-      </c>
-      <c r="J5" s="52" t="inlineStr">
-        <is>
-          <t>自然复用率 &lt; 10% 或 Saved-Prefill 收益完全被控制/传输开销抵消，无法对账复现，直接触发 No-Go 止损。</t>
-        </is>
-      </c>
-      <c r="K5" s="52" t="inlineStr">
-        <is>
-          <t>不实现生产目录、完整调度器、HA、在线学习；不把合成热点直接外推为生产承诺。</t>
-        </is>
-      </c>
-      <c r="L5" s="52" t="inlineStr">
-        <is>
-          <t>版本化 workload pack、baseline 报告、trace schema、指标字典、原始数据与一键复现实验脚本。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E0 立项充分性 评审记录。</t>
-        </is>
-      </c>
-      <c r="M5" s="52" t="inlineStr">
-        <is>
-          <t>直接演进为 IR-02-11 的 telemetry/trace 与 IR-02-12 的 perf/CI 基线，不做一次性脚本。</t>
-        </is>
-      </c>
-      <c r="N5" s="51" t="inlineStr">
-        <is>
-          <t>否（收益前提确认）</t>
-        </is>
-      </c>
-      <c r="O5" s="51" t="inlineStr">
-        <is>
-          <t>4~6人日</t>
-        </is>
-      </c>
-      <c r="P5" s="51" t="inlineStr">
-        <is>
-          <t>IR-02-11、IR-02-12</t>
-        </is>
-      </c>
-      <c r="Q5" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L3-OB-PerPathTelemetry-047、L1-OB-SemanticMetrics-016、SE-MONITOR-001、SE-PERF-001；SR23：SR23-02-11-01、SR23-02-11-02、SR23-02-12-01、SR23-02-12-05</t>
-        </is>
-      </c>
-      <c r="R5" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】Saved-Prefill 是 KVCache 存储池收益的核心前提。必须以真实业务与受控负载，实测覆盖 MLA (512B) 与 MHA (320KB) 在各复用率下的加速上限。
+【对应验证阶段】E0 业务收益确认门。</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>1 源节点，1 目的节点；涵盖 Qwen2.5-72B (MHA 320KB/tok) 与 DeepSeek-V3 (MLA 512B/tok)；复用率 30%, 50%, 70%, 90%, 98%；前缀长度 8K~128K。</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】真实/合成前缀构造 + URMA/UBMEM 对比 + 多模型矩阵消融。
+【验证方法】运行 make_workload.py 与 benchmark_serving.py 发起在线打流，采集各阶段微秒耗时。</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>2 节点直连；2 档模型 (MLA/MHA)；5 档复用率；4 档并发 (1/4/16/32)。</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>本地纯重算 baseline、官方原生 Mooncake (URMA)、深度重构扩展版 (UBMEM 零拷贝)。</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>TTFT P50/P99、Prefill 耗时、目录查询延时、传输耗时、挂接耗时、Saved-Prefill 净收益。</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>在 50% 复用率下，Saved-Prefill 净收益 ≥ 2.0× 总开销，UBMEM 加速比 ≥ 1.30×，错误消费 = 0。</t>
+        </is>
+      </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>若净收益显著，正式立项；若仅超长文本有效，设定场景白名单准入。</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="inlineStr">
+        <is>
+          <t>所有复用率下加载开销均大于本地直接重算耗时（净收益为负）。</t>
+        </is>
+      </c>
+      <c r="K5" s="52" t="n"/>
+      <c r="L5" s="52" t="n"/>
+      <c r="M5" s="52" t="n"/>
+      <c r="N5" s="51" t="n"/>
+      <c r="O5" s="51" t="n"/>
+      <c r="P5" s="51" t="n"/>
+      <c r="Q5" s="52" t="n"/>
+      <c r="R5" s="51" t="n"/>
     </row>
     <row r="6" ht="43.20000076293945" customHeight="1">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>PVT-01</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】存储池的数据平面必须建立在真实可达、零/极低 Host Payload 参与的高性能硬件通路上。若硬件介质间数据传输依赖 CPU/DDR 显式拷贝中转，或者 completion/fence/ready 不闭环，会导致性能惨跌和数据损坏。
-【与项目竞争力关联】直接支撑竞争力#3（第一方软硬件协同与 Zero-Host-Touch 直达路径）。验证 UBMEM/URMA, RDMA, C2C, NVMe/SSD 等底层硬件原语能否真正编译为 zero Host payload touch 的 KVCache 极速传输，建立硬件能力矩阵 (Capability Matrix)。
-【对应验证阶段 (E0~E3)】E1 能力路径。</t>
-        </is>
-      </c>
-      <c r="C6" s="52" t="inlineStr">
-        <is>
-          <t>覆盖 HBM↔DDR、跨节点 HBM/DDR (RDMA/URMA)、HBM↔SSD 直达/低 Host 参与容量路径。单次传输 64KB~1GB；Queue Depth 1/8/32/128；内存对齐与非对齐；正常/网络拥塞/存储高 IOPS 负载；注入超时、半写、ECC/RAS 错误与句柄失效。</t>
-        </is>
-      </c>
-      <c r="D6" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“微基准探针（Microbench Probe）+ 硬件底层计数器 Hook + 错误注入”三位一体的方法。绕过上层框架逻辑，直接对 GPU/NPU HBM、DDR、NVMe SSD 及 RDMA/URMA 网卡注册 Memory Pool，测试原生硬件 Direct 传输带宽与 CPU cycles 开销。
-【验证方法】1) 编写零拷贝 Capability Probe 测量 P50/P99 延时与有效带宽；2) Hook 操作系统/PCIe/NIC 计数器核验 Host Payload Touch 是否为 0；3) 构造 completion-&gt;fence-&gt;integrity evidence 异步确认链；4) 注入断网/半写模拟，验证 Ready 语义屏障与错误 KV 阻断。
-【方法审阅补强】除 CPU memcpy、staged 与框架原生路径外，若目标硬件已有 Mooncake/LMCache Provider，纳入同等调优对照；强制输出计划路径与实际路径凭证（实际路径凭证（ActualPathReceipt））及 主机有效载荷触碰（Host Payload Touch）。</t>
-        </is>
-      </c>
-      <c r="E6" s="52" t="inlineStr">
-        <is>
-          <t>64KB~1GB；QD 1/8/32/128；对齐/非对齐；本地/跨节点；正常/拥塞/故障；至少 1 条 SSD 容量路径。</t>
-        </is>
-      </c>
-      <c r="F6" s="52" t="inlineStr">
-        <is>
-          <t>CPU memcpy、TCP/staged、框架原生 swap/offload、同硬件空载峰值；若可用，Mooncake/LMCache 目标硬件 Provider 同等调优路径。</t>
-        </is>
-      </c>
-      <c r="G6" s="52" t="inlineStr">
-        <is>
-          <t>P50/P95/P99、effective BW/峰值比、CPU cycles/GB、Host payload bytes、CQ/fence耗时、ready延迟、retry/fallback、错误KV消费数。</t>
-        </is>
-      </c>
-      <c r="H6" s="52" t="inlineStr">
-        <is>
-          <t>至少一条热路径 (RDMA/URMA 有效带宽 ≥ 线速 80%) 和一条 HBM↔SSD 直达或低 Host 参与容量路径 (顺序带宽 ≥ 设备峰值 80%) 正确闭环；主路径 Host Payload Touch = 0，CPU 压缩/解压与全量 CPU CRC 调用 = 0，错误/半写 KV 消费 = 0。</t>
-        </is>
-      </c>
-      <c r="I6" s="52" t="inlineStr">
-        <is>
-          <t>仅 Staged (经过 CPU/DDR) 路径可用，但 CPU 额外开销 &lt; 10% 且支持显速限流，作为非默认回退路径。</t>
-        </is>
-      </c>
-      <c r="J6" s="52" t="inlineStr">
-        <is>
-          <t>无可用 HBM↔SSD 直达/低 Host 路径、Host 参与不可观测、completion/fence 异步确认失效或错误 KV 渗入推理。</t>
-        </is>
-      </c>
-      <c r="K6" s="52" t="inlineStr">
-        <is>
-          <t>不做完整 tier manager、生产HA、CPU codec/全量CPU CRC、全平台适配。</t>
-        </is>
-      </c>
-      <c r="L6" s="52" t="inlineStr">
-        <is>
-          <t>版本化 capability matrix、路径性能曲线、Host CPU 零数据拷贝对账 对账、故障注入报告、Go/禁用/回退路径表。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E1 能力路径 评审记录。</t>
-        </is>
-      </c>
-      <c r="M6" s="52" t="inlineStr">
-        <is>
-          <t>探针、注册池、句柄和microbench进入正式 Backend Provider 与CI硬件回归。</t>
-        </is>
-      </c>
-      <c r="N6" s="51" t="inlineStr">
-        <is>
-          <t>否（底座能力确认）</t>
-        </is>
-      </c>
-      <c r="O6" s="51" t="inlineStr">
-        <is>
-          <t>10~14人日</t>
-        </is>
-      </c>
-      <c r="P6" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-06、IR-01-08、IR-01-09、IR-01-12</t>
-        </is>
-      </c>
-      <c r="Q6" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L4-MC-HIER-STORE-001、L3-MS-Tiering-038、L4-HW-HostPayloadTouchBudget-076、L4-FT-PathIntegrityPolicy-077；SR23：SR23-01-06-01、SR23-01-07-01、SR23-01-08-01、SR23-01-09-01、SR23-01-12-01</t>
-        </is>
-      </c>
-      <c r="R6" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】必须确立 Host CPU 仅负责下发控制指令、不参与正文 Payload 搬运（Host Payload Touch Bytes 严格为 0）的物理底座。
+【对应验证阶段】E1 核心数据通路打通门。</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>2 节点 800G URMA/RDMA 直连；4× NVMe Gen5 SSD 阵列；涵盖 CANN P2P Pinning 显存直达与 CPU memcpy 对照。</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】P2P 显存锁定 + URMA DMA + eBPF 监控零拷贝。
+【验证方法】运行 raw_trans_bench 与 host_touch_monitor.py 抓取底层传输链路带宽与 CPU 触碰。</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>4KB~64MB 块大小；单双向读写；并发度 1~32；开启/关闭 eBPF 监控。</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>Host CPU memcpy 中转、原生 URMA DMA、UBMEM 显存直通共享、io_uring Direct I/O。</t>
+        </is>
+      </c>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>传输带宽 Gbps、P99 时延 µs、Host CPU 利用率、Host Payload Touch Bytes（eBPF 探针）。</t>
+        </is>
+      </c>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>Host CPU Payload Touch Bytes 严格为 0，800G 网络带宽利用率 ≥ 90%，自动导出 capability_matrix.json。</t>
+        </is>
+      </c>
+      <c r="I6" s="55" t="inlineStr">
+        <is>
+          <t>零拷贝底座成立，输出硬件能力矩阵进入正式调度大脑。</t>
+        </is>
+      </c>
+      <c r="J6" s="55" t="inlineStr">
+        <is>
+          <t>Host CPU 无法摆脱数据搬运，或总线争用引发严重时延恶化。</t>
+        </is>
+      </c>
+      <c r="K6" s="52" t="n"/>
+      <c r="L6" s="52" t="n"/>
+      <c r="M6" s="52" t="n"/>
+      <c r="N6" s="51" t="n"/>
+      <c r="O6" s="51" t="n"/>
+      <c r="P6" s="51" t="n"/>
+      <c r="Q6" s="52" t="n"/>
+      <c r="R6" s="51" t="n"/>
     </row>
     <row r="7" ht="43.20000076293945" customHeight="1">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>PVT-02</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】vLLM (PagedAttention block) 与 SGLang (RadixTree page/span) 的 KV 内存布局不一致。如果每次传输都需要逐块 CPU 编译提交或做格式转换，CPU 提交瓶颈与小 IO 放大将吞噬所有硬件带宽收益。
-【与项目竞争力关联】支撑竞争力#1（面向布局编译的 Descriptor 引擎）与竞争力#4（统一 QueryPlan 异步执行）。证明将不同框架逻辑布局编译为批量 Hardware Descriptors + 异步 DAG，可实现 Prefill/Decode 算力与 KV 传输的高效重叠。
-【对应验证阶段 (E0~E3)】E1 能力路径。</t>
-        </is>
-      </c>
-      <c r="C7" s="52" t="inlineStr">
-        <is>
-          <t>vLLM Paged block (16/32 tokens) 与 SGLang page/radix span；数据块 256KB~64MB；Scatter-Gather 段数 1~1024；QD 1~64；覆盖整段复用、部分前缀复用、流水中途 Cancel 与 Timeout 异常。</t>
-        </is>
-      </c>
-      <c r="D7" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“逻辑 Extent 映射 -&gt; Descriptor 批量编译 -&gt; 异步 Stream/DAG 调度”的切片验证方法。构建零拷贝 Descriptor Compiler，将上层 Paged Block 映射表一次性编译为硬件 DMA/RDMA 批量描述符链表。
-【验证方法】1) 构造典型 vLLM 与 SGLang 内存布局 Manifest；2) 运行 Descriptor 编译器计算 submit CPU cycles 与 Descriptor 数量缩减比；3) 接入 PVT-01 RDMA/SSD 后端，测量 Layer/Block 级异步流水重叠率；4) 模拟 Prefill/Decode 算力 Stream 与传输 Stream 的 Concurrent 调度。
-【方法审阅补强】对照逐块拷贝、单描述符和最佳可用开源传输实现；固定布局、对象大小、队列深度与后端，拆分编译、提交、执行和等待时间，防止用大包吞吐掩盖小 I/O 放大。</t>
-        </is>
-      </c>
-      <c r="E7" s="52" t="inlineStr">
-        <is>
-          <t>vLLM paged block + SGLang page/radix；4档对象大小；SG数量1~1024；QD 1~64；整段/部分前缀；取消/超时。</t>
-        </is>
-      </c>
-      <c r="F7" s="52" t="inlineStr">
-        <is>
-          <t>逐 block/page copy、单请求单 descriptor、整对象完成后计算；最佳可用开源批量传输实现。</t>
-        </is>
-      </c>
-      <c r="G7" s="52" t="inlineStr">
-        <is>
-          <t>descriptor数、I/O放大、submit CPU、effective BW、布局错误、batch latency、计算—传输重叠率、额外内存、取消释放时延。</t>
-        </is>
-      </c>
-      <c r="H7" s="52" t="inlineStr">
-        <is>
-          <t>Descriptor 数量下降 ≥ 50%，effective BW 提升 ≥ 30%，CPU submit 时间下降 ≥ 40%，布局协商错误 = 0，计算—传输重叠率 ≥ 60%，额外内存 ≤ 15%。</t>
-        </is>
-      </c>
-      <c r="I7" s="52" t="inlineStr">
-        <is>
-          <t>仅单一框架/布局达标时限定首发范围；不兼容路径使用显式 transform 或降级重算。</t>
-        </is>
-      </c>
-      <c r="J7" s="52" t="inlineStr">
-        <is>
-          <t>描述符编译开销过大抵消传输收益、布局协商错误不可防止，或流水调度导致 TPOT/内存严重退化。</t>
-        </is>
-      </c>
-      <c r="K7" s="52" t="inlineStr">
-        <is>
-          <t>不做通用格式转换器、全模型layout、生产级调度器或所有后端。</t>
-        </is>
-      </c>
-      <c r="L7" s="52" t="inlineStr">
-        <is>
-          <t>可复用 descriptor compiler、两后端 adapter、DAG执行器薄片、golden layout cases 与性能报告。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E1 能力路径 评审记录。</t>
-        </is>
-      </c>
-      <c r="M7" s="52" t="inlineStr">
-        <is>
-          <t>原型代码直接进入 Transfer Manager 的 Descriptor/Async DAG 子模块。</t>
-        </is>
-      </c>
-      <c r="N7" s="51" t="inlineStr">
-        <is>
-          <t>否（关键执行链确认）</t>
-        </is>
-      </c>
-      <c r="O7" s="51" t="inlineStr">
-        <is>
-          <t>10~12人日</t>
-        </is>
-      </c>
-      <c r="P7" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-02、IR-01-04</t>
-        </is>
-      </c>
-      <c r="Q7" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L3-SE-DescriptorFromManifest-079、L3-MC-LayoutTransformPlan-078、L2-OL-BulkDescriptor-025、L2-OL-LayoutNegotiation-024；SR23：SR23-01-02-01、SR23-01-04-01、SR23-02-06-01</t>
-        </is>
-      </c>
-      <c r="R7" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】对标 vLLM-Ascend 原生 Python-ZMQ 连接器，验证 64B POD C++ 描述符批量编译与跨节点 Layerwise 边算边传异步 DAG 重叠流水。
+【对应验证阶段】E1 核心数据通路打通门。</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>2 节点分布式环境；16~64 层大模型；显存离散碎片率 10%~100%；Chunked Prefill 切块粒度 512~4096 tokens。</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】64B POD 描述符贪心合并 + NPU/DMA 双 Stream 异步重叠。
+【验证方法】运行 async_dag_bench 模拟大模型逐层边算边传，抓取重叠率与提交开销。</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>3 档离散碎片率 (10%/50%/100%)；3 档 Chunk 尺寸；Compute Stream 与 Transfer Stream 异步编排。</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>vLLM-Ascend 原生 Python-ZMQ 序列化、C++ 连续块合并描述符、逐层流水重叠版。</t>
+        </is>
+      </c>
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>描述符编译耗时 µs、压缩率 %、计算耗时、传输耗时、流水总耗时、Overlap Ratio %、CPU 提交开销。</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>描述符合并压缩率 ≥ 50%，单次编译耗时 &lt; 5µs，流水重叠率 ≥ 60%，CPU 提交开销降低 ≥ 40%。</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>描述符编译器与异步流水机制正式并入 Transfer Manager 核心代码仓。</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="inlineStr">
+        <is>
+          <t>描述符编译开销超过传输收益，或异步流水导致 NPU 计算严重空转。</t>
+        </is>
+      </c>
+      <c r="K7" s="52" t="n"/>
+      <c r="L7" s="52" t="n"/>
+      <c r="M7" s="52" t="n"/>
+      <c r="N7" s="51" t="n"/>
+      <c r="O7" s="51" t="n"/>
+      <c r="P7" s="51" t="n"/>
+      <c r="Q7" s="52" t="n"/>
+      <c r="R7" s="51" t="n"/>
     </row>
     <row r="8" ht="32.40000152587891" customHeight="1">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>PVT-03</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】业界常误以为共享内存/UBMEM 语义可无脑用于所有 Active KV 的 Direct View（直接跨节点/跨进程远端读取）。然而 Decode 阶段重读 KV 会产生大量随机小访问，远端 Direct View 会导致严重 Page Fault、TLB Miss 和 Remote Stall。
-【与项目竞争力关联】支撑竞争力#1（语义先于位置与 View-vs-Copy 成本模型）及证伪验证。通过实测划清 Metadata/Snapshot 适合 Direct View 而 Decode Active KV 必须 Copy-to-HBM 的安全边界，防止盲目追求“零拷贝”反而损害 TPOT。
-【对应验证阶段 (E0~E3)】E1/E2 路径与决策边界。</t>
-        </is>
-      </c>
-      <c r="C8" s="52" t="inlineStr">
-        <is>
-          <t>元数据 (64B~64KB) 与 KV span (256KB~64MB)；单次读取 vs 连续重读；1/2/4 NPU ranks；包含 First-touch, Page size (4KB/64KB/2MB), 映射失效 (Revoke) 与并发冲突场景。</t>
-        </is>
-      </c>
-      <c r="D8" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“场景解耦对比（A/B Testing）+ 微观 Hardware Counter 监测 + View Guard 保护”的验证思路。将访问模式分为“只读元数据/快照”与“Decode 活跃 KV”两类，对比 Direct-View 与 Copy-to-HBM 的性能损耗。
-【验证方法】1) 使用 UBMEM/URMA 建立共享内存映射与 Direct View 句柄；2) 模拟 Attention 算子直接 View 远端 KV，抓取 CPU/NPU TLB Miss、Page Fault 及 Remote Stall 计数；3) 验证 Read-Only Lease 与 Revoke 机制；4) 计算 Cost Crossover 临界点。
-【方法审阅补强】按对象类型×访问模式做 直接访问（Direct View） 与 复制到 HBM（Copy-to-HBM） 配对 A/B；固定 page size、Rank 和重读次数，报告远端 stall/TLB/page fault，并以 View Guard 故障用例证明安全边界。</t>
-        </is>
-      </c>
-      <c r="E8" s="52" t="inlineStr">
-        <is>
-          <t>metadata 64B~64KB；KV span 256KB~64MB；一次读/多次重读；1/2/4 rank；first-touch、page size、并发、映射失效。</t>
-        </is>
-      </c>
-      <c r="F8" s="52" t="inlineStr">
-        <is>
-          <t>本地 hash/radix mirror、RPC 精确查询、block_table 本地执行内存、KV 显式 复制到 HBM（Copy-to-HBM）。</t>
-        </is>
-      </c>
-      <c r="G8" s="52" t="inlineStr">
-        <is>
-          <t>lookup/attach P99、每token访问P99、TPOT、remote stall、TLB/page fault、copy latency、revoke P99、stale/越界、策略准确率。</t>
-        </is>
-      </c>
-      <c r="H8" s="52" t="inlineStr">
-        <is>
-          <t>本地快判 &lt; 10us；目标 direct-view 场景 TPOT P99 回退 &lt; 3%、stale/越界 = 0、view revoke P99 &lt; 1ms，且明确划分出 Copy-vs-View 收益安全区。</t>
-        </is>
-      </c>
-      <c r="I8" s="52" t="inlineStr">
-        <is>
-          <t>只允许 metadata/attach 前只读快照 direct-view；decode-active KV 一律 copy-to-HBM。</t>
-        </is>
-      </c>
-      <c r="J8" s="52" t="inlineStr">
-        <is>
-          <t>Crossover 临界点不稳定、关键计数器不可用，或 direct-view 导致不可控远端 stall 导致 TPOT 恶化。</t>
-        </is>
-      </c>
-      <c r="K8" s="52" t="inlineStr">
-        <is>
-          <t>不做通用统一内存、写共享、跨租户共享、完整目录HA或全部模型。</t>
-        </is>
-      </c>
-      <c r="L8" s="52" t="inlineStr">
-        <is>
-          <t>对象类型×访问模式决策表、DirectViewGuard原型、lease/revoke测试、性能crossover曲线。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E1/E2 路径与决策边界 评审记录。</t>
-        </is>
-      </c>
-      <c r="M8" s="52" t="inlineStr">
-        <is>
-          <t>DirectViewGuard、对象分类与counter探针进入正式 View/Copy cost model。</t>
-        </is>
-      </c>
-      <c r="N8" s="51" t="inlineStr">
-        <is>
-          <t>是（证伪“decode-active KV 默认 direct-view”）</t>
-        </is>
-      </c>
-      <c r="O8" s="51" t="inlineStr">
-        <is>
-          <t>10~14人日</t>
-        </is>
-      </c>
-      <c r="P8" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-07、IR-02-04、IR-02-05</t>
-        </is>
-      </c>
-      <c r="Q8" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L1-OL-ViewVsCopy-011、L2-MM-ViewLease-028、L3-SE-ViewCopyCostModel-034、L3-MS-UBC2CTier-055；SR23：SR23-01-07-01、SR23-01-10-01、SR23-02-04-01、SR23-02-05-02</t>
-        </is>
-      </c>
-      <c r="R8" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】测定 Direct-View 与 Copy-to-HBM 的 Crossover 交叉临界点，实测证伪 Decode 阶段活跃 KV 直读，验证 ViewGuard SIGBUS 容错回滚。
+【对应验证阶段】E1/E2 路径与决策边界门。</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>跨节点共享内存池；重读次数 1~10 次；注入远端节点宕机/网络闪断/租约超时故障。</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】微基准 Crossover 测定 + 真实服务注入证伪 + ViewGuard 故障演练。
+【验证方法】运行 view_vs_copy_bench 与 benchmark_serving_view.py 验证决策边界。</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>重读次数 1~10；只读 vs 活跃读写；远端异常崩溃注入。</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>本地 Copy-to-HBM、跨节点 Direct-View、ViewGuard 保护模式。</t>
+        </is>
+      </c>
+      <c r="G8" s="55" t="inlineStr">
+        <is>
+          <t>单次访问耗时、累计耗时、TPOT Jitter、SIGBUS 捕获率、回滚本地重算耗时 ms。</t>
+        </is>
+      </c>
+      <c r="H8" s="55" t="inlineStr">
+        <is>
+          <t>确立重读次数 &gt; 2 时必须 Copy-to-HBM；证实 Decode 活跃 KV 直读不可行；ViewGuard 实现 100% 捕获 SIGBUS 并安全回滚。</t>
+        </is>
+      </c>
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>冻结 Direct-View 仅用于冷只读，ViewGuard 机制进入正式运行时。</t>
+        </is>
+      </c>
+      <c r="J8" s="55" t="inlineStr">
+        <is>
+          <t>Direct-View 无法安全捕获故障导致推理进程崩溃，或边界判定失真。</t>
+        </is>
+      </c>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+      <c r="M8" s="52" t="n"/>
+      <c r="N8" s="51" t="n"/>
+      <c r="O8" s="51" t="n"/>
+      <c r="P8" s="51" t="n"/>
+      <c r="Q8" s="52" t="n"/>
+      <c r="R8" s="51" t="n"/>
     </row>
     <row r="9" ht="32.40000152587891" customHeight="1">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>PVT-04</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】物理命中并不等于物理收益（Load 远端 KV 节点受拥塞/并发影响可能比本地算力 Prefill 重算更慢）。缺乏微秒级感知决策的存储池极易引发“负收益命中”和尾延迟恶化。
-【与项目竞争力关联】核心支撑竞争力#4（统一 QueryPlan 动态决策引擎）与竞争力#1（价值先于容量）。在微秒级内量化比较 Load, View, Move 与 Recompute 的实时 Cost，实现“正价值才加载，负收益即重算”。
-【对应验证阶段 (E0~E3)】E2 决策优越性。</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
-        <is>
-          <t>4 档 KV 大小 (1MB~512MB)；3 档 请求 Deadline；4 档 队列拥塞深度；包含路径正常/热点拥塞/节点断连；覆盖 Local Load, Remote Load, SSD Restore, Local Recompute。</t>
-        </is>
-      </c>
-      <c r="D9" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“离线 Oracle 轨迹对比 + 在线 Shadow QueryPlan 算法评估 + 拥塞/故障扰动”的验证方法。用低开销 EWMA 与 Hardware Telemetry 构建微秒级 Cost Evaluator，与事后最优解 (Oracle) 计算决策后悔率 (Decision Regret)。
-【验证方法】1) 收集真实硬件传输与 NPU 重算算力包络；2) 运行 QueryPlanFastPath 原型，在 &lt; 5us 内输出 Placement &amp; Action Plan；3) 注入链路拥塞与节点高负载，测试 Fallback 到重算/次优路径的决策响应；4) 统计 Cost 预测误差与错误 Load 比例。
-【方法审阅补强】同时比较静态优先级、最近副本、总是加载、总是重算和离线 Oracle；增加“关闭状态智能”和“移除非公开微架构信息”两组消融，报告 决策后悔（Decision Regret） 与错误 Load。</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="inlineStr">
-        <is>
-          <t>4档KV大小；3档deadline；4档queue depth；路径正常/退化/断开；local/remote/recompute。</t>
-        </is>
-      </c>
-      <c r="F9" s="52" t="inlineStr">
-        <is>
-          <t>固定优先级、最近副本、总是加载、总是重算、轮询、离线 Oracle；完整方案关闭状态智能/移除微架构信息两组消融。</t>
-        </is>
-      </c>
-      <c r="G9" s="52" t="inlineStr">
-        <is>
-          <t>决策P99、选择准确率、预测误差、错误Load、abandoned remote load、cross-node bytes、净TTFT benefit、故障切换、无效路径选择。</t>
-        </is>
-      </c>
-      <c r="H9" s="52" t="inlineStr">
-        <is>
-          <t>QueryPlan 决策延时 P99 &lt; 5us，Fabric Router 路由决策 &lt; 3us；路径选择准确率 ≥ 90%，成本预测误差 &lt; 20%，负收益/错误 Load &lt; 1%，无效路径选择 = 0，故障切换 &lt; 200ms。</t>
-        </is>
-      </c>
-      <c r="I9" s="52" t="inlineStr">
-        <is>
-          <t>只对白名单 prefix/路径启用动态决策；动态质量噪声过大时降级为静态优先级规则+feature flag。</t>
-        </is>
-      </c>
-      <c r="J9" s="52" t="inlineStr">
-        <is>
-          <t>尾部成本无法预测、错误 Load 持续超门槛，或复杂策略开销抵消了 Prefill 节省的时间。</t>
-        </is>
-      </c>
-      <c r="K9" s="52" t="inlineStr">
-        <is>
-          <t>不做在线学习、生产router、自动扩缩容、千卡控制面或全模型调参。</t>
-        </is>
-      </c>
-      <c r="L9" s="52" t="inlineStr">
-        <is>
-          <t>QueryPlan字段冻结稿、cost model原型、oracle对账、正收益白名单、fallback原因码。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E2 决策优越性 评审记录。</t>
-        </is>
-      </c>
-      <c r="M9" s="52" t="inlineStr">
-        <is>
-          <t>原型直接演进为 PolicyEngine/PlacementResolver，并复用路径telemetry。</t>
-        </is>
-      </c>
-      <c r="N9" s="51" t="inlineStr">
-        <is>
-          <t>否（决策能力确认）</t>
-        </is>
-      </c>
-      <c r="O9" s="51" t="inlineStr">
-        <is>
-          <t>8~10人日</t>
-        </is>
-      </c>
-      <c r="P9" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-03、IR-01-05</t>
-        </is>
-      </c>
-      <c r="Q9" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L1-RT-Admission-007、L3-SE-QueryPlanFastPath-072、L3-TRANS-TOPO-SENSE-004、L4-FABRIC-ROUTER-001；SR23：SR23-01-03-01、SR23-01-05-01、SR23-01-09-01、SR23-02-02-01、SR23-02-02-02</t>
-        </is>
-      </c>
-      <c r="R9" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】构建微秒调度大脑，在微秒级时间内根据链路状态、算力与上下文长度选择最优加载或重算路径，覆盖 MLA (512B) 与 MHA。
+【对应验证阶段】E2 动态调度决策门。</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>100K QPS 决策吞吐；涵盖 MLA 与 MHA；网络拥塞、链路降级、远端负载波动故障注入。</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】5 维成本量化模型 + 微秒级剪枝 + 反事实决策对账。
+【验证方法】运行 query_plan_bench 在 100K QPS 吞吐下压测决策引擎。</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>100K 决策样本；3 档模型架构；正常/拥塞/故障 3 档链路状态。</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>静态规则选路、全路径遍历评估、QueryPlanFastPath 微秒剪枝决策。</t>
+        </is>
+      </c>
+      <c r="G9" s="55" t="inlineStr">
+        <is>
+          <t>单次决策耗时 P50/P99 µs、决策吞吐 QPS、决策准确率 %、负收益加载拦截率 %、错误选路率 %。</t>
+        </is>
+      </c>
+      <c r="H9" s="55" t="inlineStr">
+        <is>
+          <t>决策耗时 P99 &lt; 5µs，决策准确率 ≥ 90%，负收益加载拦截率 100%，错误决策率 &lt; 1%。</t>
+        </is>
+      </c>
+      <c r="I9" s="55" t="inlineStr">
+        <is>
+          <t>决策引擎与成本模型进入正式 PolicyEngine/PlacementResolver 模块。</t>
+        </is>
+      </c>
+      <c r="J9" s="55" t="inlineStr">
+        <is>
+          <t>决策耗时超过 20µs 成为系统瓶颈，或决策准确率 &lt; 80% 导致频繁负收益加载。</t>
+        </is>
+      </c>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="52" t="n"/>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="51" t="n"/>
+      <c r="O9" s="51" t="n"/>
+      <c r="P9" s="51" t="n"/>
+      <c r="Q9" s="52" t="n"/>
+      <c r="R9" s="51" t="n"/>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>PVT-05</t>
         </is>
       </c>
-      <c r="B10" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】HBM 昂贵且容量有限，必须利用 NVMe SSD 扩展可寻址容量。但可寻址容量不等于可服务能力；若分层搬运造成 HBM 碎片、Preemption 抖动或 DDR 缓存无效命中，将严重损害 QPS 与成本效益。
-【与项目竞争力关联】核心支撑竞争力#1（分层容量与 DDR 条件角色）与竞争力#2（可服务容量与 NPU 吞吐提升）。验证“HBM↔SSD 直通为容量主路径，DDR 仅承担正收益条件角色”，确保每一 GB 扩展容量都转化为实际业务 QPS。
-【对应验证阶段 (E0~E3)】E2/E3 决策与系统净收益。</t>
-        </is>
-      </c>
-      <c r="C10" s="52" t="inlineStr">
-        <is>
-          <t>超长上下文 128K/256K/1M；容量压力 10%/30%/50%；并发 1~64；DDR 容量阶梯 (0~512GB)；包含 Hot-spot (高频重复) 与 Long-tail (长尾长上下文) 两类 Workload。</t>
-        </is>
-      </c>
-      <c r="D10" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“离线策略回放器（Replayer）+ 真实受控物理介质压测”相结合的验证思路。对比 HBM↔SSD 直达、HBM→DDR→SSD 三级传递、DDR Warm/Prefetch 等不同架构模式下的吞吐与延迟。
-【验证方法】1) 运行 Trace 驱动的容量策略回放器，对比 LRU, LFU, Cost-aware 淘汰算法；2) 在真实 HBM+DDR+SSD 硬件节点配置受控内存/存储水位；3) 测量 HBM 有效容量提升、OOM/Preemption 降低率与 SSD 读写 IOPS/写放大；4) 评估 DDR 引入后的净收益 (Cost-Benefit Ratio)。
-【方法审阅补强】比较简单双水位、LRU/LFU 与成本策略；除容量和命中外同步报告 TPOT、SSD IOPS/写放大、功耗和单位 SLO 合格事务成本，防止成本转移。</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="inlineStr">
-        <is>
-          <t>128K/256K/1M；容量压力10%/30%/50%；3档并发；DDR容量阶梯；热点/长尾两类workload。</t>
-        </is>
-      </c>
-      <c r="F10" s="52" t="inlineStr">
-        <is>
-          <t>框架原生容量/水位/preemption、SSD-only、LRU、双水位滞回；完整方案关闭状态智能的消融。</t>
-        </is>
-      </c>
-      <c r="G10" s="52" t="inlineStr">
-        <is>
-          <t>HBM effective capacity、稳定并发/QPS、OOM/preemption、碎片、usable hit、迁移bytes/ping-pong、SSD P99、DDR staging bytes、端到端hop时延、DDR GB/BW、单位有效容量成本、NPU busy/stall。</t>
-        </is>
-      </c>
-      <c r="H10" s="52" t="inlineStr">
-        <is>
-          <t>HBM↔SSD 容量主路径闭环且有效带宽 ≥ 设备峰值 80%；HBM 有效容量提升 ≥ 30%，OOM/Preemption 降低 ≥ 50%，内存碎片率 &lt; 5%；DDR 角色至少有一项持续正收益，否则退出 Payload 主路径；迁移 Bytes 降低 ≥ 20%。</t>
-        </is>
-      </c>
-      <c r="I10" s="52" t="inlineStr">
-        <is>
-          <t>若 DDR 无独立正收益，仅保留 DDR 用于 Metadata/Control/Registered Pool，Payload 保持 HBM↔SSD 直达。</t>
-        </is>
-      </c>
-      <c r="J10" s="52" t="inlineStr">
-        <is>
-          <t>SSD 扩容带来的迁移抖动使端到端 TTFT/TPOT 净收益为负，或碎片率 &gt; 15% 导致频繁 Preemption。</t>
-        </is>
-      </c>
-      <c r="K10" s="52" t="inlineStr">
-        <is>
-          <t>不实现生产tier manager、跨节点副本编排、在线学习、自动调参和完整defrag。</t>
-        </is>
-      </c>
-      <c r="L10" s="52" t="inlineStr">
-        <is>
-          <t>容量—服务能力曲线、DDR角色决策、策略回放器、模型KV规格表、水位/回退默认值。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E2/E3 决策与系统净收益 评审记录。</t>
-        </is>
-      </c>
-      <c r="M10" s="52" t="inlineStr">
-        <is>
-          <t>回放器与策略接口进入TierManager；实验结论冻结硬件容量和人力投入边界。</t>
-        </is>
-      </c>
-      <c r="N10" s="51" t="inlineStr">
-        <is>
-          <t>否（容量价值确认）</t>
-        </is>
-      </c>
-      <c r="O10" s="51" t="inlineStr">
-        <is>
-          <t>10~14人日</t>
-        </is>
-      </c>
-      <c r="P10" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-01、IR-02-08、IR-02-09</t>
-        </is>
-      </c>
-      <c r="Q10" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L3-MS-Tiering-038、L3-MC-HIER-STORE-002、L3-MS-DDRRolePolicy-092、L3-SE-TierBypassPolicy-091；SR23：SR23-01-01-01、SR23-01-01-02、SR23-01-01-03、SR23-01-08-01、SR23-02-08-01、SR23-02-09-01</t>
-        </is>
-      </c>
-      <c r="R10" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】对标 Mooncake 原生文件级 SSD Offload，验证 Linux 6.6+ io_uring FIXED I/O 裸盘直达容量主路径，在显存超载下实现安全扩容。
+【对应验证阶段】E2 分层扩容与容量门。</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>4× NVMe Gen5 SSD 裸盘；100%~200% HBM 显存超载；64 并发请求；4KB 对齐扇区管理。</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】裸盘 4KB 对齐管理 + io_uring Direct I/O + 水位线驱动异步沉淀。
+【验证方法】运行 tier_storage_bench 与 benchmark_tiering.py 进行超载压测。</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>100%, 150%, 200% 显存超载；文件系统 offload vs io_uring 裸盘直达；高低水位线 (85%/65%) 触发。</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>纯 HBM 基线、Host DDR Staging 中转、Mooncake 原生 SSD 文件 Offload、io_uring FIXED 裸盘直达。</t>
+        </is>
+      </c>
+      <c r="G10" s="55" t="inlineStr">
+        <is>
+          <t>服务 Token 总量、OOM 发生次数、请求驱逐率、SSD 读写吞吐 GB/s、Host DDR 触碰字节。</t>
+        </is>
+      </c>
+      <c r="H10" s="55" t="inlineStr">
+        <is>
+          <t>在 150% 显存超载下，可服务容量提升 ≥ 30%，OOM 降低 ≥ 50%，SSD 吞吐达线速 ≥ 80%，全程 Bypass DDR。</t>
+        </is>
+      </c>
+      <c r="I10" s="55" t="inlineStr">
+        <is>
+          <t>裸盘直达容量主路径成立，TierBlockAllocator 进入正式分层存储管理模块。</t>
+        </is>
+      </c>
+      <c r="J10" s="55" t="inlineStr">
+        <is>
+          <t>SSD 换入换出引发前台严重抖动，或无法绕过 Host DDR。</t>
+        </is>
+      </c>
+      <c r="K10" s="52" t="n"/>
+      <c r="L10" s="52" t="n"/>
+      <c r="M10" s="52" t="n"/>
+      <c r="N10" s="51" t="n"/>
+      <c r="O10" s="51" t="n"/>
+      <c r="P10" s="51" t="n"/>
+      <c r="Q10" s="52" t="n"/>
+      <c r="R10" s="51" t="n"/>
     </row>
     <row r="11" ht="43.20000076293945" customHeight="1">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>PVT-06</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】物理 Raw Hit 绝不等于可安全消费的 Usable Hit。若 KV 存在版本冲突、Layout 不匹配、Rank 未对齐、未 Ready 或 Lease 过期，强行消费将导致输出胡言乱语、死锁甚至跨租户数据泄露事故。
-【与项目竞争力关联】核心支撑竞争力#1（语义先于位置与 Ready/Eligibility 屏障）与竞争力#2（0 错误消费正确性安全底线）。构建完整的 ConsumeEligibility 与 Rank Consensus 校验机制，确保“0 错误消费、0 过期消费”。
-【对应验证阶段 (E0~E3)】E1 可消费正确性。</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr">
-        <is>
-          <t>Whole (100%), Partial (25%/50%/75%) 前缀复用；1/2/4/8 Tensor/Pipeline Parallel Ranks；注入 Model/Tokenizer/ChatTemplate/Adapter/Layout/Version 冲突、Ready 未完成、Lease 失效与单 Rank 故障。</t>
-        </is>
-      </c>
-      <c r="D11" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“语义契约断言校验 + 故障/冲突全量注入 + 张量并行 (TP=8) 多卡状态同步 (RankConsensus)”的硬核正确性验证思路。设计 Reason-Code 判定引擎，对每一个 Candidate KV 进行 6 维 Eligibility 检查。
-【验证方法】1) 构造全套正确的 Golden Cases 与带冲突的 Fault Injection Cases；2) 运行 ConsumeEligibility &amp; AttachHandle 校验模块；3) 验证多 Rank 间 RankConsensus 屏障与 Wait 时延；4) 统计 Raw Hit 到 Usable Hit 的转化漏斗与 Duplicate Pull 合并效率。
-【方法审阅补强】使用 Golden/Fault 全矩阵覆盖版本、布局、Ready、Lease、Rank 和跨租户；与原生/最佳开源连接器的兼容与回退行为对照，任何错误消费均直接 No-Go。</t>
-        </is>
-      </c>
-      <c r="E11" s="52" t="inlineStr">
-        <is>
-          <t>whole/25%/50%/75% partial hit；1/2/4 rank；ready延迟、版本冲突、lease失效、单rank故障。</t>
-        </is>
-      </c>
-      <c r="F11" s="52" t="inlineStr">
-        <is>
-          <t>raw hash hit 直接消费、全量重算、无重复拉取合并；原生连接器与最佳可行开源连接器的兼容/回退对照。</t>
-        </is>
-      </c>
-      <c r="G11" s="52" t="inlineStr">
-        <is>
-          <t>raw/usable/stale/abandoned/fallback漏斗、错误消费、prefix lookup P99、attach P99、rank wait、duplicate pull、effective reused tokens、recompute tokens、fallback恢复时间。</t>
-        </is>
-      </c>
-      <c r="H11" s="52" t="inlineStr">
-        <is>
-          <t>错误/过期 KV 消费数 = 0，Fallback 成功率 = 100%，Rank Consensus Wait P99 &lt; 100us，Prefix Lookup P99 &lt; 200us，Usable Hit 提升 ≥ 15%，重复拉取下降 ≥ 50%。</t>
-        </is>
-      </c>
-      <c r="I11" s="52" t="inlineStr">
-        <is>
-          <t>仅开放同模型/同版本/同 Layout 的 Whole-Prefix 或 Min-Safe-Prefix 消费白名单。</t>
-        </is>
-      </c>
-      <c r="J11" s="52" t="inlineStr">
-        <is>
-          <t>发生任何错误/脏 KV 渗入推理、跨租户越权读取或多 Rank 同步死锁。</t>
-        </is>
-      </c>
-      <c r="K11" s="52" t="inlineStr">
-        <is>
-          <t>不实现完整目录HA、跨租户共享、全量多卡故障恢复或生产调度。</t>
-        </is>
-      </c>
-      <c r="L11" s="52" t="inlineStr">
-        <is>
-          <t>兼容性矩阵、ConsumeEligibility/AttachHandle原型、reason code、故障用例和漏斗报告。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E1 可消费正确性 评审记录。</t>
-        </is>
-      </c>
-      <c r="M11" s="52" t="inlineStr">
-        <is>
-          <t>协议、判定器、golden cases与fault tests进入Connector/Directory正式模块。</t>
-        </is>
-      </c>
-      <c r="N11" s="51" t="inlineStr">
-        <is>
-          <t>否（可消费性确认）</t>
-        </is>
-      </c>
-      <c r="O11" s="51" t="inlineStr">
-        <is>
-          <t>10~12人日</t>
-        </is>
-      </c>
-      <c r="P11" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-10、IR-01-11、IR-02-01、IR-02-05</t>
-        </is>
-      </c>
-      <c r="Q11" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L2-KV-AttachHandle-034、L2-KV-PartialAttachPlan-038、L3-MS-ConsumeEligibility-060、L3-CO-VisibilityReadyBitmap-064、L1-PD-RankConsensus-013；SR23：SR23-01-10-01、SR23-01-11-01、SR23-02-01-01、SR23-02-05-01、SR23-02-05-02、SR23-02-10-01</t>
-        </is>
-      </c>
-      <c r="R11" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】验证 6 维语义（模型/词表/模板/LoRA/Ready/Lease）微秒级强校验，杜绝脏读；验证 TP=8 张量并行多卡共享内存状态同步耗时 P99 &lt; 100µs。
+【对应验证阶段】E1 核心数据通路打通门。</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>TP=8 多卡物理节点；注入 8 类语义冲突（模型不匹配/Tokenizer冲突/模板漂移/LoRA失效/半写脏块/租约过期等）；部分命中前缀拼接。</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】xxHash64 6 维校验 + POSIX /dev/shm 共享内存状态广播 + 协同 Fallback。
+【验证方法】运行 rank_consensus_bench 与 test_correctness.py 进行故障注入。</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>8 类语义冲突用例；TP=8 多卡并行；部分命中 (20%~80%) 拼接。</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>无校验直读、部分校验、6 维语义全量强校验 + POSIX 共享内存多卡同步。</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>冲突拦截率 %、错误消费次数、6 维校验耗时 µs、TP=8 多卡同步耗时 P99 µs、输出 Token 正确率 %。</t>
+        </is>
+      </c>
+      <c r="H11" s="55" t="inlineStr">
+        <is>
+          <t>8 类语义冲突拦截率 100%，错误消费严格为 0；TP=8 多卡状态同步耗时 P99 &lt; 100µs，杜绝死锁。</t>
+        </is>
+      </c>
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>校验引擎与多卡共识协议进入正式 Connector 与 Directory 核心模块。</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="inlineStr">
+        <is>
+          <t>出现脏读或未就绪数据消费，或多卡状态同步耗时超过 500µs 导致通信死锁。</t>
+        </is>
+      </c>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+      <c r="N11" s="51" t="n"/>
+      <c r="O11" s="51" t="n"/>
+      <c r="P11" s="51" t="n"/>
+      <c r="Q11" s="52" t="n"/>
+      <c r="R11" s="51" t="n"/>
     </row>
     <row r="12" ht="32.40000152587891" customHeight="1">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>PVT-07</t>
         </is>
       </c>
-      <c r="B12" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】单项传输带宽或局部算法达标，不代表在线系统成功。在真实在线推理中，前台 Decode 算力/带宽与后台 SSD 回源、预取、迁移混压，极易引发 IO 争用与 TPOT 尾部严重抖动。
-【与项目竞争力关联】终极支撑竞争力#2（端到端净收益与端到端最小闭环验证 (Vertical Slice)验收）与竞争力#4（前后台 Semantic QoS 隔离）。作为立项前最后一个“纵向切片”总门禁，在真实混压下验证 TTFT/TPOT/QPS 整体净收益。
-【对应验证阶段 (E0~E3)】E3 系统净收益。</t>
-        </is>
-      </c>
-      <c r="C12" s="52" t="inlineStr">
-        <is>
-          <t>2 节点环境，1 个典型主模型；前台 3 档并发 × 后台 4 档传输带宽 混压；覆盖 Steady State 与 Burst 突发；包含长上下文与共享前缀两类 Workload；包含无隔离、软件限流与硬件独立队列/TC 3 组对照。</t>
-        </is>
-      </c>
-      <c r="D12" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“真实前后台混压（Co-location Stress）+ 端到端纵向切片（Vertical Slice）+ 前后台服务质量保障策略 (SemanticQoS)判定”的闭环验证思路。串联 Prefix Lookup -&gt; QueryPlan -&gt; Descriptor -&gt; Load/Attach/Recompute 全流程。
-【验证方法】1) 建立包含前台 Decode 推理与后台 SSD 回源/Prefetch 的混压环境；2) 运行 Semantic QoS 调度策略，设定前后台优先级与限速包络；3) 抓取端到端 TTFT P50/P99、TPOT P50/P99/Tail Spike、QPS 及 NPU Busy/Stall；4) 执行 Fallback 演练。
-【方法审阅补强】在同硬件、同模型、同 SLO、同调优预算下比较原生框架、最佳可行开源组合、本项目关闭状态智能、本项目移除微架构信息及完整方案；以实际路径、合格业务事务和全生命周期成本给出净收益。</t>
-        </is>
-      </c>
-      <c r="E12" s="52" t="inlineStr">
-        <is>
-          <t>3档前台并发×4档后台带宽×burst/steady；正常/拥塞/单路径故障；长上下文与共享前缀两类workload。</t>
-        </is>
-      </c>
-      <c r="F12" s="52" t="inlineStr">
-        <is>
-          <t>框架原生路径、最佳可行开源组合、统一池关闭 QoS/流水、本项目关闭状态智能、本项目移除微架构信息、总是加载与重算。</t>
-        </is>
-      </c>
-      <c r="G12" s="52" t="inlineStr">
-        <is>
-          <t>TTFT P50/P99、TPOT P50/P99/tail spike、QPS、NPU busy/stall、overlap、前后台BW/QD、abandoned load、fallback、恢复时间。</t>
-        </is>
-      </c>
-      <c r="H12" s="52" t="inlineStr">
-        <is>
-          <t>端到端 P99 TTFT 降低 ≥ 20%，SemanticQoS 受控子测试 P99 TTFT 降低 ≥ 25%；QPS 提升 ≥ 10%，计算与传输重叠率 ≥ 60%，安全包络内 TPOT P99 回退 &lt; 3%，Fallback 成功率 = 100%。</t>
-        </is>
-      </c>
-      <c r="I12" s="52" t="inlineStr">
-        <is>
-          <t>仅在低水位/空闲时段允许后台 SSD 恢复/预取，或对远端 Load 施加严格白名单。</t>
-        </is>
-      </c>
-      <c r="J12" s="52" t="inlineStr">
-        <is>
-          <t>后台 IO 造成前台 TPOT 尾抖动 &gt; 10%，或端到端系统开销完全吞噬了 TTFT 收益。</t>
-        </is>
-      </c>
-      <c r="K12" s="52" t="inlineStr">
-        <is>
-          <t>不实现生产QoS控制器、全网调度、多租户计费、生产HA和全模型适配。</t>
-        </is>
-      </c>
-      <c r="L12" s="52" t="inlineStr">
-        <is>
-          <t>可运行端到端最小闭环验证 (Vertical Slice)、干扰安全包络、性能分解、fallback演练、项目级Go/Conditional/No-Go结论。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 E3 系统净收益 评审记录。</t>
-        </is>
-      </c>
-      <c r="M12" s="52" t="inlineStr">
-        <is>
-          <t>端到端最小闭环验证 (Vertical Slice) 成为首个系统串联与回归场景；QoS分类、指标和fallback接口直接进入正式系统。</t>
-        </is>
-      </c>
-      <c r="N12" s="51" t="inlineStr">
-        <is>
-          <t>否（项目价值总门禁）</t>
-        </is>
-      </c>
-      <c r="O12" s="51" t="inlineStr">
-        <is>
-          <t>12~15人日</t>
-        </is>
-      </c>
-      <c r="P12" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-04、IR-01-11、IR-02-06</t>
-        </is>
-      </c>
-      <c r="Q12" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L3-QO-SemanticQoS-045、L3-MS-StateAwarePrefetch-081、L3-OB-PerPathTelemetry-047、L4-FT-PathIntegrityPolicy-077；SR23：SR23-01-04-01、SR23-01-11-02、SR23-02-02-01、SR23-02-02-02、SR23-02-06-01、SR23-02-11-01、SR23-02-12-03、SR23-02-12-05</t>
-        </is>
-      </c>
-      <c r="R12" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】在真实 2 节点集群、前台在线推理与后台 400G I/O 满载混压下，串联全流程，实施三重消融对账，确立立项总门禁。
+【对应验证阶段】E3 全链路前后台混压总门禁。</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>2 节点集群（Node-0 Prefill, Node-1 Decode）；800G 网络直连；前台 32 并发在线打流 + 后台 400G 满载 I/O 混压。</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】2 节点真实集群 + 官方 benchmark_serving.py 在线打流 + 三重消融总门禁。
+【验证方法】运行 deploy_cluster.sh 与 run_mixed_bench.py 执行全链路压测。</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>纯前台在线基线、原生 Mooncake+Ascend 混压基线、深度重构扩展版 (SemanticQoS 优先级队列与自适应退避)。</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>原生推理基线、官方原生 Mooncake 混压、Unified KV 深度重构扩展版混压。</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="inlineStr">
+        <is>
+          <t>全链路 TTFT P50/P99 ms、TPOT P50/P99 ms、TPOT Jitter 干扰率 %、系统 QPS、NPU 算力利用率。</t>
+        </is>
+      </c>
+      <c r="H12" s="55" t="inlineStr">
+        <is>
+          <t>深度重构扩展版相比原生 Mooncake，全链路 P99 TTFT 降低 ≥ 20%，QPS 提升 ≥ 10%，前台 P99 TPOT 干扰率严格 &lt; 3%。</t>
+        </is>
+      </c>
+      <c r="I12" s="55" t="inlineStr">
+        <is>
+          <t>全量达标则签署立项准入，端到端最小闭环作为生产回归基准。</t>
+        </is>
+      </c>
+      <c r="J12" s="55" t="inlineStr">
+        <is>
+          <t>前台 TPOT 干扰率 ≥ 10%，或 TTFT 相比原生 Mooncake 无显著收益，项目否决关闭。</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="n"/>
+      <c r="L12" s="52" t="n"/>
+      <c r="M12" s="52" t="n"/>
+      <c r="N12" s="51" t="n"/>
+      <c r="O12" s="51" t="n"/>
+      <c r="P12" s="51" t="n"/>
+      <c r="Q12" s="52" t="n"/>
+      <c r="R12" s="51" t="n"/>
     </row>
     <row r="13" ht="21.60000038146973" customHeight="1">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>PVT-08</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】覆盖公共系统提示词广播、Multi-Agent 共享上下文分发、PD 分离 1P-to-ND 分叉三大业务场景，验证软件 Staging 组播相比单播源端带宽节省 ≥ 60%。
+【对应验证阶段】E1 拓展分发拓扑验证门。</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>1 个源 Prefill 节点，2/4/8 个目的 Decode 节点；热点 Prefix 16MB~128MB；单播 vs 软件 Staging 树状组播 vs 硬件多播对比。</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】三大场景流量编排 + 单播 vs 软件 Staging 树状分发 vs 硬件多播对比。
+【验证方法】运行 multicast_fanout_bench.cc 测量不同节点规模下的分发时延与带宽。</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>2, 4, 8 目的节点；2 档 Prefix 大小 (16MB/64MB)；正常与慢节点/单点故障注入。</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>N 次独立单播拉取、软件 Staging 树状中继组播、硬件网络多播（若环境支持）。</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>源端 Egress 流量与带宽占用、各 Consumer 接收完成时间 P99、慢节点拖尾影响、源端 CPU 开销。</t>
+        </is>
+      </c>
+      <c r="H13" s="55" t="inlineStr">
+        <is>
+          <t>在 1-to-8 分发下，软件 Staging 组播相比单播源端带宽节省 ≥ 60%，传输耗时降低 ≥ 40%，且在硬件多播不可用时作为主力路径。</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="inlineStr">
+        <is>
+          <t>软件 Staging 组播机制正式并入 Transfer Manager 组播子模块，主路径不强依赖硬件多播。</t>
+        </is>
+      </c>
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t>软件组播协议开销过大导致尾延迟显著恶化，或带宽节省 &lt; 30%。</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="n"/>
+      <c r="L13" s="52" t="n"/>
+      <c r="M13" s="52" t="n"/>
+      <c r="N13" s="51" t="n"/>
+      <c r="O13" s="51" t="n"/>
+      <c r="P13" s="51" t="n"/>
+      <c r="Q13" s="52" t="n"/>
+      <c r="R13" s="51" t="n"/>
+    </row>
+    <row r="14" ht="21.60000038146973" customHeight="1">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>PVT-09</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】确立公有云可信 VPC 下 Raw Direct 纯软主路径与企业级专线下 DPU 硬件线速 AES/CRC 卸载的双轨体系；验证 500µs 无缝降级；提前布局 Fly-in-line 在途处理。
+【对应验证阶段】E1 底座支撑与双轨验证门。</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>配置企业级 800G DPU 智能网卡；开启硬件 AES-256-GCM / SM4 加密与 CRC64 校验；注入 DPU 驱动挂死与控制超时故障。</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】Raw Direct 基线 + DPU 硬件加速 A/B 测试 + 500µs 降级演练 + Fly-in-line 架构布局。
+【验证方法】运行 offload_fallback_bench 与 inject_dpu_fault.py 演练双轨切换。</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>2 档对象大小 (1MB/16MB)；3 档并发；DPU 硬件加速 vs Raw Direct 纯软直达；DPU 超时故障注入。</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>Raw Direct 裸机直达路径、DPU 硬件线速安全卸载路径、Host CPU 软算（负面对照）。</t>
+        </is>
+      </c>
+      <c r="G14" s="55" t="inlineStr">
+        <is>
+          <t>Host CPU 占用率、传输吞吐 Gbps、端到端时延、DPU 故障检测耗时、无缝降级耗时 µs、数据完整性校验正确率。</t>
+        </is>
+      </c>
+      <c r="H14" s="55" t="inlineStr">
+        <is>
+          <t>DPU 硬件线速完成安全卸载（CPU 占用降低 ≥ 30%）；故障时在 &lt; 500µs 内无缝降级至 Raw Direct 裸机直达路径，业务不中断。</t>
+        </is>
+      </c>
+      <c r="I14" s="55" t="inlineStr">
+        <is>
+          <t>双轨切换机制并入正式 Backend Provider，主路径保持 0 DPU 强依赖可运行。</t>
+        </is>
+      </c>
+      <c r="J14" s="55" t="inlineStr">
+        <is>
+          <t>DPU 卸载引入额外时延恶化，或发生故障时无法安全回退导致请求失败。</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="n"/>
+      <c r="L14" s="52" t="n"/>
+      <c r="M14" s="52" t="n"/>
+      <c r="N14" s="51" t="n"/>
+      <c r="O14" s="51" t="n"/>
+      <c r="P14" s="51" t="n"/>
+      <c r="Q14" s="52" t="n"/>
+      <c r="R14" s="51" t="n"/>
+    </row>
+    <row r="15" ht="32.40000152587891" customHeight="1">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>CVT-01</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】业界常推崇硬件多播 (Multicast) 用于热点前缀分发。但硬件多播配置复杂且依赖网络支持，必须验证节点级 Staging / 软件 Fanout 是否已足够满足要求，证伪硬件多播的“硬依赖”假象。
-【与项目竞争力关联】支撑竞争力#5（开放生态与简洁架构）及条件证伪。明确 1→N 共享的 Crossover 点，避免在立项早期过度投入复杂硬件多播。
-【对应验证阶段 (E0~E3)】条件证伪门。</t>
-        </is>
-      </c>
-      <c r="C13" s="52" t="inlineStr">
-        <is>
-          <t>1 源节点，2/4/8 消费者节点；热点 Prefix 对象 1MB~64MB；比较独立 N 次拉取、软件 Staging Fanout、硬件多播（若环境支持）；包含正常与慢消费者/单节点故障。</t>
-        </is>
-      </c>
-      <c r="D13" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“Fanout 规模阶梯对比 + 传输放大系数测量 + 硬件多播必要性证伪”的验证思路。
-【验证方法】1) 构造不同 Fanout 比例的并发拉取请求；2) 测量源端 egress 带宽与各 Consumer 端完成时间 P99；3) 评估软件 Staging 与硬件多播的收益差距；4) 判定 Fanout Crossover 临界点。
-【方法审阅补强】仅在 Fanout 分布和重复远端字节达到触发门后执行；比较 N 次独立拉取、软件 Staging 和硬件多播，硬件能力无稳定增量即关闭。</t>
-        </is>
-      </c>
-      <c r="E13" s="52" t="inlineStr">
-        <is>
-          <t>固定热点prefix；2档对象大小；正常/慢消费者/单目标故障。</t>
-        </is>
-      </c>
-      <c r="F13" s="52" t="inlineStr">
-        <is>
-          <t>N 次独立拉取、软件 Staging Fanout、硬件多播（若平台可用）。</t>
-        </is>
-      </c>
-      <c r="G13" s="52" t="inlineStr">
-        <is>
-          <t>源端bytes、完成P99、consumer skew、重复拉取、refcount/lease泄漏、源端CPU/BW。</t>
-        </is>
-      </c>
-      <c r="H13" s="52" t="inlineStr">
-        <is>
-          <t>重复远端拉取流量下降 ≥ 50%，源端带宽增长显著低于 O(N)，错误共享/泄漏 = 0。</t>
-        </is>
-      </c>
-      <c r="I13" s="52" t="inlineStr">
-        <is>
-          <t>硬件多播无额外净收益时，默认保留软件 Node-level Staging Fanout。</t>
-        </is>
-      </c>
-      <c r="J13" s="52" t="inlineStr">
-        <is>
-          <t>Fanout 收益无法覆盖多播协议握手与尾延迟开销。</t>
-        </is>
-      </c>
-      <c r="K13" s="52" t="inlineStr">
-        <is>
-          <t>不做全局热度预测、生产多播控制面和自动副本生命周期。</t>
-        </is>
-      </c>
-      <c r="L13" s="52" t="inlineStr">
-        <is>
-          <t>fanout crossover、feature flag建议和回退策略。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 条件证伪门 评审记录。</t>
-        </is>
-      </c>
-      <c r="M13" s="52" t="inlineStr">
-        <is>
-          <t>仅Go后进入Async DAG的可选Multicast Provider。</t>
-        </is>
-      </c>
-      <c r="N13" s="51" t="inlineStr">
-        <is>
-          <t>是（证伪“硬件多播是关键IR前置条件”）</t>
-        </is>
-      </c>
-      <c r="O13" s="51" t="inlineStr">
-        <is>
-          <t>6~8人日（触发后）</t>
-        </is>
-      </c>
-      <c r="P13" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-04、IR-01-10</t>
-        </is>
-      </c>
-      <c r="Q13" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L4-RDMA-MUL-FABRIC-002；SR23：SR23-01-04-02、SR23-01-10-01</t>
-        </is>
-      </c>
-      <c r="R13" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21.60000038146973" customHeight="1">
-      <c r="A14" s="51" t="inlineStr">
-        <is>
-          <t>CVT-02</t>
-        </is>
-      </c>
-      <c r="B14" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】内存页迁移/压缩时，业界探索硬件 Atomic Remap 原语。需验证软件 RCU (Read-Copy-Update) + Copy-on-Migrate 是否已能满足 Pause 与抖动要求，优先证伪硬件原语的“必需性”。
-【与项目竞争力关联】支撑竞争力#3（第一方软硬件协同的理性边界）。防范盲目依赖未成熟硬件原语导致架构套牢。
-【对应验证阶段 (E0~E3)】条件证伪门。</t>
-        </is>
-      </c>
-      <c r="C14" s="52" t="inlineStr">
-        <is>
-          <t>单 Extent，1/8/32 并发 Reader；数据块 4MB~64MB；比较 Stop-the-world, 软件 RCU, 硬件 Atomic Remap；注入 Remap 前/中/后崩溃故障。</t>
-        </is>
-      </c>
-      <c r="D14" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采用“读写并发压测 + Pause 抖动抓取 + 失败回滚演练”的验证思路。
-【验证方法】1) 在 Reader 持续读取 KV 时触发 Extent 迁移/整理；2) 测量 Reader 的 Pause 时间 P99 与 TPOT Jitter；3) 注入 Remap 中途中断，验证崩溃回滚；4) 评估 RCU 与硬件 Remap 的增量收益。
-【方法审阅补强】以软件 RCU + Copy-on-Migrate 为默认基线，覆盖并发读、故障中断、回滚和 TLB shootdown；硬件 Remap 只接受可重复的增量收益。</t>
-        </is>
-      </c>
-      <c r="E14" s="52" t="inlineStr">
-        <is>
-          <t>3档extent；1/8/32 reader；remap前/中/后故障。</t>
-        </is>
-      </c>
-      <c r="F14" s="52" t="inlineStr">
-        <is>
-          <t>Stop-the-world、软件 RCU + Copy-on-Migrate、硬件 Atomic Remap（若可用）。</t>
-        </is>
-      </c>
-      <c r="G14" s="52" t="inlineStr">
-        <is>
-          <t>stale/use-after-free、pause P99、TPOT jitter、remap、TLB shootdown、回滚。</t>
-        </is>
-      </c>
-      <c r="H14" s="52" t="inlineStr">
-        <is>
-          <t>脏读/越界访问 = 0，迁移 TPOT 抖动 &lt; 5%，失败 100% 可回滚，且硬件 Remap 相对 RCU 有稳定净收益。</t>
-        </is>
-      </c>
-      <c r="I14" s="52" t="inlineStr">
-        <is>
-          <t>硬件收益不显著时，正式架构固定使用软件 RCU + Copy-on-Migrate。</t>
-        </is>
-      </c>
-      <c r="J14" s="52" t="inlineStr">
-        <is>
-          <t>硬件 Remap 语义不成熟、无法可靠回滚或引发 TLB Shootdown 惩罚。</t>
-        </is>
-      </c>
-      <c r="K14" s="52" t="inlineStr">
-        <is>
-          <t>不实现完整defrag、跨节点迁移编排或生产allocator。</t>
-        </is>
-      </c>
-      <c r="L14" s="52" t="inlineStr">
-        <is>
-          <t>RCU基线、硬件原语No-Go/Go结论、迁移互锁接口。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 条件证伪门 评审记录。</t>
-        </is>
-      </c>
-      <c r="M14" s="52" t="inlineStr">
-        <is>
-          <t>仅Go后把硬件remap作为feature-flag后端；RCU原型直接保留。</t>
-        </is>
-      </c>
-      <c r="N14" s="51" t="inlineStr">
-        <is>
-          <t>是（优先证伪硬件原语必要性）</t>
-        </is>
-      </c>
-      <c r="O14" s="51" t="inlineStr">
-        <is>
-          <t>8~12人日（触发后）</t>
-        </is>
-      </c>
-      <c r="P14" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-01、IR-01-11、IR-01-12</t>
-        </is>
-      </c>
-      <c r="Q14" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L4-CO-AtomicRemapPrimitive-065、L3-CO-MigrationRCULock-090；SR23：SR23-01-01-03、SR23-01-11-01、SR23-01-12-02</t>
-        </is>
-      </c>
-      <c r="R14" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32.40000152587891" customHeight="1">
-      <c r="A15" s="51" t="inlineStr">
-        <is>
-          <t>CVT-03</t>
-        </is>
-      </c>
-      <c r="B15" s="52" t="inlineStr">
-        <is>
-          <t>【背景与必要性】评估 DPU 卸载、硬件 CQ 路由与硬件 Codec 压缩的真实价值。需明确项目在无 DPU/Codec 时必须按 Raw/Direct 路径完全成立，且严禁使用 Host CPU 软件压缩/全量 CPU CRC 填补缺口。
-【与项目竞争力关联】支撑竞争力#3（第一方责任与防伪解耦）及能力降级验证。确保主路径纯粹高效，任何卸载只能是“纯增量”而非“硬依附”。
-【对应验证阶段 (E0~E3)】条件证伪门。</t>
-        </is>
-      </c>
-      <c r="C15" s="52" t="inlineStr">
-        <is>
-          <t>2 档对象大小 (1MB/16MB)；3 档并发；对比 Raw/Direct 路径 vs DPU CQ/Route 卸载 vs 硬件 Codec；包含卸载通道故障与 Host CPU 占用对照（严禁 CPU 软件压缩做主路径）。</t>
-        </is>
-      </c>
-      <c r="D15" s="52" t="inlineStr">
-        <is>
-          <t>【验证思路】采取“Raw Direct 基线对比 + DPU/Codec 硬件卸载 A/B 测试 + CPU 软解压对比防误区”的验证思路。
-【验证方法】1) 以 PVT-01 Raw Direct 路径为绝对 Baseline；2) 接入 DPU/硬件 Codec，测量 Host CPU 卸载比例与 CQ 提交延时；3) 故意关闭 DPU/Codec，测试无缝 Fallback 到 Raw Direct 路径；4) 评估 CPU 软件 Codec 对 CPU 的吞噬副作用。
-【方法审阅补强】以无 DPU/Codec 的 原始直达（Raw Direct） 为必须成立基线；DPU/Codec 只验证纯增量并执行关闭/故障旁路，禁止以 CPU 软件编解码伪造收益。</t>
-        </is>
-      </c>
-      <c r="E15" s="52" t="inlineStr">
-        <is>
-          <t>2档对象大小；3档并发；正常/卸载故障；raw与硬件codec。</t>
-        </is>
-      </c>
-      <c r="F15" s="52" t="inlineStr">
-        <is>
-          <t>Host 仅控制提交且不触碰 Payload 的 原始直达（Raw Direct）；DPU/CQ/硬件 Codec；CPU 软件 Codec 仅作为负面对照，不得作为回退。</t>
-        </is>
-      </c>
-      <c r="G15" s="52" t="inlineStr">
-        <is>
-          <t>Host CPU、CQ latency、route lookup、压缩比/吞吐、额外时延、TPOT、fallback、Host CPU 零数据拷贝对账。</t>
-        </is>
-      </c>
-      <c r="H15" s="52" t="inlineStr">
-        <is>
-          <t>Host CPU 占用下降 ≥ 30%，端到端净收益为正，故障可无损旁路到 Raw Direct，Host Payload Touch 不增加。</t>
-        </is>
-      </c>
-      <c r="I15" s="52" t="inlineStr">
-        <is>
-          <t>仅卸载 CQ/路由或仅用于冷数据后台存储，硬件缺失时保持 Raw Direct 运行。</t>
-        </is>
-      </c>
-      <c r="J15" s="52" t="inlineStr">
-        <is>
-          <t>卸载增加额外的 PCIe/DMA 延迟，或尝试改用 CPU 软件压缩/CRC 来伪造卸载效果。</t>
-        </is>
-      </c>
-      <c r="K15" s="52" t="inlineStr">
-        <is>
-          <t>明确排除CPU压缩/解压、CPU全量CRC与DDR codec工作区。</t>
-        </is>
-      </c>
-      <c r="L15" s="52" t="inlineStr">
-        <is>
-          <t>Not Supported/Go报告、能力表、feature flag与旁路方案。
-竞争力证据最小集：冻结基线、重复实验、实际路径/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、异常结果、适用边界及 条件证伪门 评审记录。</t>
-        </is>
-      </c>
-      <c r="M15" s="52" t="inlineStr">
-        <is>
-          <t>仅Go后作为Backend Provider可选插件；主路径保持无DPU可运行。</t>
-        </is>
-      </c>
-      <c r="N15" s="51" t="inlineStr">
-        <is>
-          <t>是（证伪“DPU/codec是项目必需依赖”）</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="inlineStr">
-        <is>
-          <t>5~8人日（触发后）</t>
-        </is>
-      </c>
-      <c r="P15" s="51" t="inlineStr">
-        <is>
-          <t>IR-01-08、IR-01-09</t>
-        </is>
-      </c>
-      <c r="Q15" s="52" t="inlineStr">
-        <is>
-          <t>SRS：L4-MC-HIER-STORE-002、L4-MC-HIER-STORE-003、L4-NET-OFFLOAD-DPU-001、L4-FT-PathIntegrityPolicy-077；SR23：SR23-01-08-01、SR23-01-08-02、SR23-01-09-01、SR23-01-12-01</t>
-        </is>
-      </c>
-      <c r="R15" s="51" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-    </row>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>【背景与必要性】验证在显存整理与页迁移时，软件 RCU + Copy-on-Migrate 是否已能满足 Pause &lt; 1ms 要求，证明无需强依赖专有硬件 AtomicRemap 芯片。
+【对应验证阶段】条件证伪门。</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>单 Extent，1/8/32 并发 Reader；数据块 4MB~64MB；比较 Stop-the-world 全局锁表 vs 软件 RCU vs 硬件 AtomicRemap。</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>【验证思路】并发读写压测 + Pause 抖动抓取 + 软硬件收益对比证伪。
+【验证方法】运行 rcu_migration_bench.cc 测量高并发 Reader 下的迁移停顿与 Jitter。</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>3 档 Extent 大小；1, 8, 32 并发 Reader；迁移中途崩溃故障注入。</t>
+        </is>
+      </c>
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>Stop-the-world 全局锁表、软件 RCU + Copy-on-Migrate、硬件 Atomic Remap（若平台支持）。</t>
+        </is>
+      </c>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>Reader 停顿时间 P99 µs、TPOT Jitter 抖动率 %、脏读/越界访问次数、迁移失败回滚耗时。</t>
+        </is>
+      </c>
+      <c r="H15" s="55" t="inlineStr">
+        <is>
+          <t>在 32 并发 Reader 下，软件 RCU 读停顿时间 P99 &lt; 1ms，TPOT 抖动率 &lt; 3%，免除对专有硬件 AtomicRemap 芯片的强依赖。</t>
+        </is>
+      </c>
+      <c r="I15" s="55" t="inlineStr">
+        <is>
+          <t>软件 RCU 原型作为显存整理与动态页迁移的正式核心机制保留，否定硬件 AtomicRemap 的硬依赖。</t>
+        </is>
+      </c>
+      <c r="J15" s="55" t="inlineStr">
+        <is>
+          <t>软件 RCU 无法保障无锁读一致性产生脏读，或停顿时间超过 10ms。</t>
+        </is>
+      </c>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+      <c r="N15" s="51" t="n"/>
+      <c r="O15" s="51" t="n"/>
+      <c r="P15" s="51" t="n"/>
+      <c r="Q15" s="52" t="n"/>
+      <c r="R15" s="51" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Q2"/>
@@ -3334,7 +2949,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>V2.3.1 需求树 IR—提前验证追溯矩阵</t>
+          <t>24条IR全量覆盖与10 PVT + 1 CVT 追溯矩阵（Mooncake 原厂扩展版 V2.0）</t>
         </is>
       </c>
     </row>
@@ -3345,7 +2960,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -3577,7 +3191,7 @@
       </c>
       <c r="E8" s="48" t="inlineStr">
         <is>
-          <t>决定计算传输重叠与在线尾时延</t>
+          <t>PVT-02、PVT-07、PVT-08</t>
         </is>
       </c>
       <c r="F8" s="48" t="inlineStr">
@@ -3785,7 +3399,7 @@
       </c>
       <c r="E12" s="48" t="inlineStr">
         <is>
-          <t>SSD容量层和低成本扩容硬门槛</t>
+          <t>PVT-01、PVT-09</t>
         </is>
       </c>
       <c r="F12" s="48" t="inlineStr">
@@ -3837,7 +3451,7 @@
       </c>
       <c r="E13" s="48" t="inlineStr">
         <is>
-          <t>多后端统一与可审计降级硬门槛</t>
+          <t>PVT-01、PVT-08、PVT-09</t>
         </is>
       </c>
       <c r="F13" s="48" t="inlineStr">
@@ -3889,7 +3503,7 @@
       </c>
       <c r="E14" s="48" t="inlineStr">
         <is>
-          <t>共享收益与故障恢复关键支撑</t>
+          <t>PVT-06、PVT-08</t>
         </is>
       </c>
       <c r="F14" s="48" t="inlineStr">
@@ -3941,7 +3555,7 @@
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
-          <t>一致性与前后台QoS上线硬门槛</t>
+          <t>PVT-06、PVT-07、CVT-01</t>
         </is>
       </c>
       <c r="F15" s="48" t="inlineStr">
@@ -3993,7 +3607,7 @@
       </c>
       <c r="E16" s="48" t="inlineStr">
         <is>
-          <t>错误KV不可消费的正确性硬门槛</t>
+          <t>PVT-01、PVT-07、PVT-09、CVT-01</t>
         </is>
       </c>
       <c r="F16" s="48" t="inlineStr">
@@ -4696,7 +4310,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -5592,12 +5205,12 @@
       </c>
       <c r="C25" s="48" t="inlineStr">
         <is>
-          <t>条件合并/证伪</t>
+          <t>升级为必须验证包</t>
         </is>
       </c>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>CVT-03</t>
+          <t>PVT-09</t>
         </is>
       </c>
       <c r="E25" s="48" t="inlineStr">
@@ -5607,12 +5220,12 @@
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>无真实硬件能力不启动，且项目不得依赖codec。</t>
+          <t>DPU硬件安全与算力卸载加速 vs Raw Direct双轨体系，布局Fly-in-line扩展</t>
         </is>
       </c>
       <c r="G25" s="48" t="inlineStr">
         <is>
-          <t>否（触发后申请）</t>
+          <t>是 (PVT-09)</t>
         </is>
       </c>
       <c r="H25" s="48" t="inlineStr">
@@ -5634,12 +5247,12 @@
       </c>
       <c r="C26" s="48" t="inlineStr">
         <is>
-          <t>条件保留/证伪</t>
+          <t>升级为必须验证包</t>
         </is>
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>CVT-01</t>
+          <t>PVT-08</t>
         </is>
       </c>
       <c r="E26" s="48" t="inlineStr">
@@ -5649,12 +5262,12 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>只有真实fanout证据触发；优先证伪硬件多播必要性。</t>
+          <t>覆盖公共提示词广播、Multi-Agent与1P-to-ND分发场景，升级为必做项</t>
         </is>
       </c>
       <c r="G26" s="48" t="inlineStr">
         <is>
-          <t>否（触发后申请）</t>
+          <t>是 (PVT-08)</t>
         </is>
       </c>
       <c r="H26" s="48" t="inlineStr">
@@ -5681,7 +5294,7 @@
       </c>
       <c r="D27" s="48" t="inlineStr">
         <is>
-          <t>CVT-02</t>
+          <t>CVT-01</t>
         </is>
       </c>
       <c r="E27" s="48" t="inlineStr">
@@ -5691,12 +5304,12 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>只有迁移pause成为瓶颈时触发，软件RCU为默认。</t>
+          <t>原CVT-02重新编号为CVT-01，验证软件RCU机制以证伪硬件AtomicRemap芯片依赖</t>
         </is>
       </c>
       <c r="G27" s="48" t="inlineStr">
         <is>
-          <t>否（触发后申请）</t>
+          <t>条件触发 (CVT-01)</t>
         </is>
       </c>
       <c r="H27" s="48" t="inlineStr">
@@ -5718,12 +5331,12 @@
       </c>
       <c r="C28" s="48" t="inlineStr">
         <is>
-          <t>条件合并/证伪</t>
+          <t>升级为必须验证包</t>
         </is>
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>CVT-03</t>
+          <t>PVT-09</t>
         </is>
       </c>
       <c r="E28" s="48" t="inlineStr">
@@ -5733,12 +5346,12 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>DPU是可选Provider，不是主路径依赖。</t>
+          <t>DPU硬件卸载与500µs无缝降级，并入PVT-09双轨验证</t>
         </is>
       </c>
       <c r="G28" s="48" t="inlineStr">
         <is>
-          <t>否（触发后申请）</t>
+          <t>是 (PVT-09)</t>
         </is>
       </c>
       <c r="H28" s="48" t="inlineStr">
@@ -5812,7 +5425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5833,7 +5446,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>立项前向技术/项目/人力主管提交的证据包</t>
+          <t>立项前向技术/项目/人力主管提交的证据包模板（10 PVT + 1 CVT 全量覆盖）</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5457,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -5913,477 +5525,320 @@
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>PVT-00</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>【E0 立项充分性】目标业务是否真的存在足够的可复用前缀与 saved-prefill 收益；后续所有原型结果能否用同一 workload、trace 和时钟口径复现并对账。</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>【E0 业务收益前提】目标业务是否存在显著 Saved-Prefill 净收益；MLA (512B) 与 MHA (320KB) 在各复用率下的协议加速边界。</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
         <is>
           <t>IR-02-11、IR-02-12</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>直接演进为 IR-02-11 的 telemetry/trace 与 IR-02-12 的 perf/CI 基线，不做一次性脚本。</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>版本化 workload pack、baseline 报告、trace schema、指标字典、原始数据与一键复现实验脚本。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K5" s="22" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L5" s="22" t="str"/>
-      <c r="M5" s="22" t="str"/>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>直接演进为 IR-02-11 的 telemetry/trace 与 IR-02-12 的 CI 性能基线。</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="22" t="n"/>
     </row>
     <row r="6" ht="92" customHeight="1">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>PVT-01</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>【E1 能力路径】UBMEM/URMA、RDMA、C2C、NVMe/SSD 能否形成至少一条热路径，以及一条不强制经过DDR的HBM↔SSD直达或低Host参与容量主路径；每条路径的Host参与、完成可见性和完整性证据是否可接受。</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
+        <is>
+          <t>【E1 物理传输底座】CANN P2P Pinning、800G URMA/UBMEM 与 NVMe 直达能否确立 Host CPU 零数据拷贝（Host Payload Touch Bytes 严格为 0）。</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>IR-01-06、IR-01-08、IR-01-09、IR-01-12</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>探针、注册池、句柄和microbench进入正式 Backend Provider 与CI硬件回归。</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>版本化 capability matrix、路径性能曲线、Host CPU 零数据拷贝对账 对账、故障注入报告、Go/禁用/回退路径表。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L6" s="23" t="str"/>
-      <c r="M6" s="23" t="str"/>
+      <c r="D6" s="59" t="inlineStr">
+        <is>
+          <t>探针、注册池、句柄和 microbench 进入正式 Backend Provider。</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="23" t="n"/>
     </row>
     <row r="7" ht="92" customHeight="1">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>PVT-02</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>【E1 能力路径】不同框架的逻辑 KV block/page/radix span 能否被稳定编译为各路径可执行的批量描述符，并与 Prefill/Decode 形成可取消、可回退的流水。</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>【E1 数据通路与流水】异构框架 Layout 能否被 C++ 描述符编译器高效贪心合并（压缩率 ≥ 50%），并打通跨节点 Layerwise 边算边传异步 DAG 重叠流水。</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>IR-01-02、IR-01-04</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>原型代码直接进入 Transfer Manager 的 Descriptor/Async DAG 子模块。</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>可复用 descriptor compiler、两后端 adapter、DAG执行器薄片、golden layout cases 与性能报告。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L7" s="23" t="str"/>
-      <c r="M7" s="23" t="str"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
     </row>
     <row r="8" ht="92" customHeight="1">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>PVT-03</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>【E1/E2 路径与决策边界】哪些对象适合 UBMEM/共享内存语义直接访问，哪些必须 local mirror 或 copy-to-HBM；decode-active KV direct-view 是否应成为默认路径。</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
+        <is>
+          <t>【E1/E2 路径与决策边界】测定 Direct-View 与 Copy-to-HBM 的 Crossover 临界点；实测证伪 Decode 活跃 KV 直读；ViewGuard 实现 100% SIGBUS 捕获与安全回滚。</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>IR-01-07、IR-02-04、IR-02-05</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>DirectViewGuard、对象分类与counter探针进入正式 View/Copy cost model。</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>对象类型×访问模式决策表、DirectViewGuard原型、lease/revoke测试、性能crossover曲线。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L8" s="23" t="str"/>
-      <c r="M8" s="23" t="str"/>
+      <c r="D8" s="59" t="inlineStr">
+        <is>
+          <t>DirectViewGuard、对象分类与探针进入正式 View/Copy cost model。</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
     </row>
     <row r="9" ht="92" customHeight="1">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>PVT-04</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>【E2 决策优越性】系统能否在微秒级用真实路径成本识别正收益命中，选择正确副本/路径，并在拥塞或故障时有界回退。</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
+        <is>
+          <t>【E2 动态调度决策】微秒级动态决策引擎能否在 P99 &lt; 5µs 内识别正收益命中，覆盖 MLA 与 MHA 成本模型，负收益拦截率 100%，错误决策率 &lt; 1%。</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>IR-01-03、IR-01-05</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>原型直接演进为 PolicyEngine/PlacementResolver，并复用路径telemetry。</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>QueryPlan字段冻结稿、cost model原型、oracle对账、正收益白名单、fallback原因码。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L9" s="23" t="str"/>
-      <c r="M9" s="23" t="str"/>
+      <c r="D9" s="59" t="inlineStr">
+        <is>
+          <t>原型直接演进为 PolicyEngine/PlacementResolver，复用 telemetry。</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
     </row>
     <row r="10" ht="92" customHeight="1">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>PVT-05</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>【E2/E3 决策与系统净收益】HBM↔SSD直达或低Host参与通路能否成为默认容量主路径并转化为可服务容量与NPU利用率；DDR应承担哪些可证明正收益的条件角色；复杂分层策略是否优于简单水位策略。</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>【E2 分层扩容与容量】HBM-SSD io_uring FIXED 裸盘直达容量主路径能否在 150% 显存超载下提升可服务容量 ≥ 30%，OOM 降低 ≥ 50%，全程 Bypass DDR。</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>IR-01-01、IR-02-08、IR-02-09</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>回放器与策略接口进入TierManager；实验结论冻结硬件容量和人力投入边界。</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>容量—服务能力曲线、DDR角色决策、策略回放器、模型KV规格表、水位/回退默认值。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L10" s="23" t="str"/>
-      <c r="M10" s="23" t="str"/>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>回放器与策略接口进入 TierManager，冻结硬件容量投入边界。</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
     </row>
     <row r="11" ht="92" customHeight="1">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>PVT-06</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>【E1 可消费正确性】前缀候选能否在版本、layout、ready、lease、rank等约束下被安全消费；部分命中与故障回退是否仍有净收益。</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>【E1 语义强校验与多卡共识】6 维语义（模型/词表/模板/LoRA/Ready/Lease）微秒级强校验拦截率 100%；TP=8 多卡 POSIX 共享内存状态同步耗时 P99 &lt; 100µs。</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
         <is>
           <t>IR-01-10、IR-01-11、IR-02-01、IR-02-05</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>协议、判定器、golden cases与fault tests进入Connector/Directory正式模块。</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>兼容性矩阵、ConsumeEligibility/AttachHandle原型、reason code、故障用例和漏斗报告。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L11" s="23" t="str"/>
-      <c r="M11" s="23" t="str"/>
+      <c r="D11" s="59" t="inlineStr">
+        <is>
+          <t>协议、判定器、golden cases 与 fault tests 进入 Connector/Directory 正式模块。</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
     </row>
     <row r="12" ht="92" customHeight="1">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>PVT-07</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>【E3 系统净收益】在真实前台Decode与后台SSD回源、预取、迁移混压下，统一池能否改善TTFT、容量和NPU利用率，同时把TPOT尾部退化控制在业务门槛内。</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>【E3 全链路混压总门禁】2 节点真实集群前台在线推理 + 后台 400G I/O 满载混压下，全链路 P99 TTFT 降低 ≥ 20%，QPS 提升 ≥ 10%，前台 P99 TPOT 干扰率 &lt; 3%。</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>IR-01-04、IR-01-11、IR-02-06</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>端到端最小闭环验证 (Vertical Slice) 成为首个系统串联与回归场景；QoS分类、指标和fallback接口直接进入正式系统。</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>可运行端到端最小闭环验证 (Vertical Slice)、干扰安全包络、性能分解、fallback演练、项目级Go/Conditional/No-Go结论。；补充同条件公平基线、关键消融、实际路径凭证（ActualPathReceipt）/Host CPU 零数据拷贝凭证（Host Payload Touch Bytes 严格为 0）、重复实验置信和异常结果。</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>待判定</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="inlineStr">
-        <is>
-          <t>待评审</t>
-        </is>
-      </c>
-      <c r="L12" s="23" t="str"/>
-      <c r="M12" s="23" t="str"/>
-    </row>
+      <c r="D12" s="59" t="inlineStr">
+        <is>
+          <t>端到端最小闭环成为首个系统串联与回归场景；QoS 分类与接口进入正式系统。</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>PVT-08</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>【E1 拓展组播拓扑】1-to-N 组播分发在公共提示词广播、Multi-Agent 与 1P-to-ND 场景下，软件 Staging 组播相比单播源端带宽节省 ≥ 60%，传输耗时降 ≥ 40%。</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>IR-01-04、IR-01-10</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>软件 Staging 拓扑管理与树状分发算法进入 Transfer Manager 组播子模块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>PVT-09</t>
+        </is>
+      </c>
+      <c r="B14" s="61" t="inlineStr">
+        <is>
+          <t>【E1 底座与双轨协同】DPU 硬件线速 AES/CRC 卸载降低 CPU 占用 ≥ 30%；发生故障时在 &lt; 500µs 内无缝降级至 Raw Direct 裸机直达路径；布局 Fly-in-line 双轨手段。</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>IR-01-08、IR-01-09、IR-01-12</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>双轨切换引擎与安全卸载插件进入 Backend Provider 模块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>CVT-01</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>【条件证伪门】在 32 并发 Reader 下，软件 RCU 显存整理读停顿时间 P99 &lt; 1ms，TPOT 抖动率 &lt; 3%，免除对专有硬件 AtomicRemap 芯片的强依赖。</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="inlineStr">
+        <is>
+          <t>IR-01-01、IR-01-11、IR-01-12</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>软件 RCU 原型作为显存整理与动态页迁移的正式核心机制保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
@@ -6429,18 +5884,17 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>建议实施波次、依赖关系与退出门</t>
+          <t>建议实施波次、依赖关系与退出门（10 PVT + 1 CVT 优先级排期）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="41" t="inlineStr">
         <is>
-          <t>总日历建议 4～5 周；PVT 共享一套 harness、冻结 workload 与 2 节点环境，CVT 不进入默认排期。W0～W3 依次关闭 E0/E1、E1/E2、E2、E3，并在 W3 完成最佳开源基线与关键消融总对账。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>总日历建议 4～5 周；PVT 共享一套 harness、冻结 workload 与 2 节点环境，CVT 按触发执行。W0～W3 依次关闭 E0/E1、E1/E2、E2、E3，并在 W3 完成原生 Mooncake 开源基线与深度重构扩展版关键消融总对账。</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -6501,7 +5955,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>PVT-00、PVT-01</t>
+          <t>PVT-00 (🟡 P1)、PVT-01 (🟡 P1)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -6548,7 +6002,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>PVT-02、PVT-03、PVT-04</t>
+          <t>PVT-02 (🔴 P0)、PVT-03 (🟡 P1)、PVT-04 (🔴 P0)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -6595,7 +6049,7 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>PVT-05、PVT-06</t>
+          <t>PVT-05 (🔴 P0)、PVT-06 (🔴 P0)、PVT-08 (🟢 P2)、PVT-09 (🟡 P1)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -6642,7 +6096,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>PVT-07</t>
+          <t>PVT-07 (🔴 P0, 全链路前后台混压端到端总门禁)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -6689,7 +6143,7 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>CVT-01~03</t>
+          <t>CVT-01 (🟢 P2, 软件 RCU 证伪硬件 AtomicRemap)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -6738,7 +6192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6764,7 +6218,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -6958,7 +6411,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>默认8个必做包；条件项不预占人力</t>
+          <t>默认 10 个必做包；1 个条件证伪项不预占主线人力</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -7098,7 +6551,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
@@ -7200,6 +6652,22 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>基于V3.2竞争力分析报告，全面增强各前置验证需求的背景诉求与竞争力关联；新增'主要验证思路与验证方法'列；精细定义测试验证范围；给出基于SLO合格事务与TCO净收益的Go/No-Go显式退出门槛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V1.6→V2.0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>全面对齐 Mooncake 高性能原厂扩展版 (Unified KV) 研发战略与立项评审意见：
+1. 升级原 CVT-01 为 PVT-08（1-to-N 组播分发：覆盖公共提示词广播、Multi-Agent 与 1P-to-ND）；
+2. 升级原 CVT-03 为 PVT-09（DPU 硬件安全卸载加速 vs Raw Direct 双轨验证，含 Fly-in-line 扩展布局）；
+3. 原 CVT-02 重编为 CVT-01（软件 RCU 机制证伪硬件 AtomicRemap）；
+4. 引入 P0/P1/P2 三级穿刺优先级，支持 DeepSeek MLA (512B) 与 Qwen MHA 双轨参数，打通 benchmark_serving 在线打流消融。</t>
         </is>
       </c>
     </row>
@@ -7238,7 +6706,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>工作簿质量、V2.3.1 需求树与四个核心验证阶段 (E0~E3) 验证目标对齐门禁（V1.6）</t>
+          <t>工作簿质量、V2.3.1 需求树与四个核心验证阶段 (E0~E3) 验证目标对齐门禁（V2.0）</t>
         </is>
       </c>
     </row>
@@ -7249,7 +6717,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -7297,8 +6764,10 @@
         <f>COUNTIF('精简验证总表'!$D$5:$D$15,"立项前必做")</f>
         <v/>
       </c>
-      <c r="D5" s="47" t="n">
-        <v>8</v>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E5" s="47">
         <f>IF(C5=D5,"PASS","FAIL")</f>
@@ -7306,7 +6775,7 @@
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>严格控制为8个共享原型包</t>
+          <t>严格控制为 10 个必做原型验证包 (PVT-00 ~ PVT-09)</t>
         </is>
       </c>
     </row>
@@ -7325,8 +6794,10 @@
         <f>COUNTIF('精简验证总表'!$D$5:$D$15,"条件/证伪")</f>
         <v/>
       </c>
-      <c r="D6" s="48" t="n">
-        <v>3</v>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E6" s="48">
         <f>IF(C6=D6,"PASS","FAIL")</f>
@@ -7334,7 +6805,7 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>不进入默认人力与排期</t>
+          <t>严格控制为 1 个条件证伪项 (CVT-01)</t>
         </is>
       </c>
     </row>
